--- a/Sp26BevoTunesSeedingData.xlsx
+++ b/Sp26BevoTunesSeedingData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mj32663\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nusu-my.sharepoint.com/personal/e1122784_u_nus_edu/Documents/Y3S2SEP/MIS 333K Web Application Development/FP/G6_BevoTunes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D92A4440-1757-48FB-8D53-9693AA2F50DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{D92A4440-1757-48FB-8D53-9693AA2F50DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED136562-69DC-D749-A468-378D306E44FA}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="23240" windowHeight="13880" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Songs" sheetId="1" r:id="rId1"/>
@@ -4603,24 +4603,28 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4628,6 +4632,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4684,7 +4689,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -4712,7 +4717,6 @@
     <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -5043,18 +5047,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O301"/>
-  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.15625" style="4"/>
-    <col min="2" max="2" width="58.41796875" style="4" customWidth="1"/>
-    <col min="3" max="3" width="9.15625" style="4"/>
-    <col min="4" max="4" width="59.15625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="19.68359375" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="44.26171875" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.15625" style="4"/>
+    <col min="1" max="1" width="9.1640625" style="4"/>
+    <col min="2" max="2" width="58.5" style="4" customWidth="1"/>
+    <col min="3" max="3" width="9.1640625" style="4"/>
+    <col min="4" max="4" width="59.1640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="19.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="44.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.1640625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" s="22" t="s">
         <v>1</v>
       </c>
@@ -5091,7 +5095,7 @@
       <c r="N1" s="6"/>
       <c r="O1" s="22"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="22" t="s">
         <v>11</v>
       </c>
@@ -5122,7 +5126,7 @@
       <c r="N2" s="22"/>
       <c r="O2" s="22"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="22" t="s">
         <v>17</v>
       </c>
@@ -5157,7 +5161,7 @@
       <c r="N3" s="22"/>
       <c r="O3" s="22"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="22" t="s">
         <v>23</v>
       </c>
@@ -5186,7 +5190,7 @@
       <c r="N4" s="22"/>
       <c r="O4" s="22"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="22" t="s">
         <v>28</v>
       </c>
@@ -5223,7 +5227,7 @@
       <c r="N5" s="22"/>
       <c r="O5" s="22"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="22" t="s">
         <v>37</v>
       </c>
@@ -5254,7 +5258,7 @@
       <c r="N6" s="22"/>
       <c r="O6" s="22"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="22" t="s">
         <v>41</v>
       </c>
@@ -5287,7 +5291,7 @@
       <c r="N7" s="22"/>
       <c r="O7" s="22"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="22" t="s">
         <v>46</v>
       </c>
@@ -5316,7 +5320,7 @@
       <c r="N8" s="22"/>
       <c r="O8" s="22"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="22" t="s">
         <v>49</v>
       </c>
@@ -5347,7 +5351,7 @@
       <c r="N9" s="22"/>
       <c r="O9" s="22"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="22" t="s">
         <v>54</v>
       </c>
@@ -5380,7 +5384,7 @@
       <c r="N10" s="22"/>
       <c r="O10" s="22"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="22" t="s">
         <v>60</v>
       </c>
@@ -5413,7 +5417,7 @@
       <c r="N11" s="22"/>
       <c r="O11" s="22"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="22" t="s">
         <v>65</v>
       </c>
@@ -5444,7 +5448,7 @@
       <c r="N12" s="22"/>
       <c r="O12" s="22"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="22" t="s">
         <v>69</v>
       </c>
@@ -5475,7 +5479,7 @@
       <c r="N13" s="22"/>
       <c r="O13" s="22"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="22" t="s">
         <v>73</v>
       </c>
@@ -5508,7 +5512,7 @@
       <c r="N14" s="22"/>
       <c r="O14" s="22"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="22" t="s">
         <v>78</v>
       </c>
@@ -5537,7 +5541,7 @@
       <c r="N15" s="22"/>
       <c r="O15" s="22"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="22" t="s">
         <v>81</v>
       </c>
@@ -5568,7 +5572,7 @@
       <c r="N16" s="22"/>
       <c r="O16" s="22"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" s="22" t="s">
         <v>85</v>
       </c>
@@ -5601,7 +5605,7 @@
       <c r="N17" s="22"/>
       <c r="O17" s="22"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" s="22" t="s">
         <v>89</v>
       </c>
@@ -5632,7 +5636,7 @@
       <c r="N18" s="22"/>
       <c r="O18" s="22"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19" s="22" t="s">
         <v>94</v>
       </c>
@@ -5669,7 +5673,7 @@
       <c r="N19" s="22"/>
       <c r="O19" s="22"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" s="22" t="s">
         <v>100</v>
       </c>
@@ -5702,7 +5706,7 @@
       <c r="N20" s="22"/>
       <c r="O20" s="22"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" s="22" t="s">
         <v>106</v>
       </c>
@@ -5733,7 +5737,7 @@
       <c r="N21" s="22"/>
       <c r="O21" s="22"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" s="22" t="s">
         <v>111</v>
       </c>
@@ -5764,7 +5768,7 @@
       <c r="N22" s="22"/>
       <c r="O22" s="22"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" s="22" t="s">
         <v>113</v>
       </c>
@@ -5795,7 +5799,7 @@
       <c r="N23" s="22"/>
       <c r="O23" s="22"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" s="22" t="s">
         <v>116</v>
       </c>
@@ -5824,7 +5828,7 @@
       <c r="N24" s="22"/>
       <c r="O24" s="22"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25" s="22" t="s">
         <v>120</v>
       </c>
@@ -5859,7 +5863,7 @@
       <c r="N25" s="22"/>
       <c r="O25" s="22"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" s="22" t="s">
         <v>126</v>
       </c>
@@ -5892,7 +5896,7 @@
       <c r="N26" s="22"/>
       <c r="O26" s="22"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27" s="22" t="s">
         <v>131</v>
       </c>
@@ -5923,7 +5927,7 @@
       <c r="N27" s="22"/>
       <c r="O27" s="22"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28" s="22" t="s">
         <v>135</v>
       </c>
@@ -5960,7 +5964,7 @@
       <c r="N28" s="22"/>
       <c r="O28" s="22"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A29" s="22" t="s">
         <v>138</v>
       </c>
@@ -5993,7 +5997,7 @@
       <c r="N29" s="22"/>
       <c r="O29" s="22"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A30" s="22" t="s">
         <v>142</v>
       </c>
@@ -6024,7 +6028,7 @@
       <c r="N30" s="22"/>
       <c r="O30" s="22"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A31" s="22" t="s">
         <v>144</v>
       </c>
@@ -6057,7 +6061,7 @@
       <c r="N31" s="22"/>
       <c r="O31" s="22"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A32" s="22" t="s">
         <v>148</v>
       </c>
@@ -6088,7 +6092,7 @@
       <c r="N32" s="22"/>
       <c r="O32" s="22"/>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A33" s="22" t="s">
         <v>152</v>
       </c>
@@ -6123,7 +6127,7 @@
       <c r="N33" s="22"/>
       <c r="O33" s="22"/>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A34" s="22" t="s">
         <v>156</v>
       </c>
@@ -6158,7 +6162,7 @@
       <c r="N34" s="22"/>
       <c r="O34" s="22"/>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A35" s="22" t="s">
         <v>160</v>
       </c>
@@ -6191,7 +6195,7 @@
       <c r="N35" s="22"/>
       <c r="O35" s="22"/>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A36" s="22" t="s">
         <v>162</v>
       </c>
@@ -6224,7 +6228,7 @@
       <c r="N36" s="22"/>
       <c r="O36" s="22"/>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A37" s="22" t="s">
         <v>165</v>
       </c>
@@ -6259,7 +6263,7 @@
       <c r="N37" s="22"/>
       <c r="O37" s="22"/>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A38" s="22" t="s">
         <v>170</v>
       </c>
@@ -6292,7 +6296,7 @@
       <c r="N38" s="22"/>
       <c r="O38" s="22"/>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A39" s="22" t="s">
         <v>173</v>
       </c>
@@ -6327,7 +6331,7 @@
       <c r="N39" s="22"/>
       <c r="O39" s="22"/>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A40" s="22" t="s">
         <v>179</v>
       </c>
@@ -6358,7 +6362,7 @@
       <c r="N40" s="22"/>
       <c r="O40" s="22"/>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A41" s="22" t="s">
         <v>182</v>
       </c>
@@ -6393,7 +6397,7 @@
       <c r="N41" s="22"/>
       <c r="O41" s="22"/>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A42" s="22" t="s">
         <v>186</v>
       </c>
@@ -6422,7 +6426,7 @@
       <c r="N42" s="22"/>
       <c r="O42" s="22"/>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A43" s="22" t="s">
         <v>190</v>
       </c>
@@ -6459,7 +6463,7 @@
       <c r="N43" s="22"/>
       <c r="O43" s="22"/>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A44" s="22" t="s">
         <v>194</v>
       </c>
@@ -6490,7 +6494,7 @@
       <c r="N44" s="22"/>
       <c r="O44" s="22"/>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A45" s="22" t="s">
         <v>198</v>
       </c>
@@ -6525,7 +6529,7 @@
       <c r="N45" s="22"/>
       <c r="O45" s="22"/>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A46" s="22" t="s">
         <v>202</v>
       </c>
@@ -6556,7 +6560,7 @@
       <c r="N46" s="22"/>
       <c r="O46" s="22"/>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A47" s="22" t="s">
         <v>206</v>
       </c>
@@ -6587,7 +6591,7 @@
       <c r="N47" s="22"/>
       <c r="O47" s="22"/>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A48" s="22" t="s">
         <v>210</v>
       </c>
@@ -6618,7 +6622,7 @@
       <c r="N48" s="22"/>
       <c r="O48" s="22"/>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A49" s="22" t="s">
         <v>213</v>
       </c>
@@ -6651,7 +6655,7 @@
       <c r="N49" s="22"/>
       <c r="O49" s="22"/>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A50" s="22" t="s">
         <v>216</v>
       </c>
@@ -6682,7 +6686,7 @@
       <c r="N50" s="22"/>
       <c r="O50" s="22"/>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51" s="22" t="s">
         <v>220</v>
       </c>
@@ -6713,7 +6717,7 @@
       <c r="N51" s="22"/>
       <c r="O51" s="22"/>
     </row>
-    <row r="52" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="52" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" s="22" t="s">
         <v>223</v>
       </c>
@@ -6742,7 +6746,7 @@
       <c r="N52" s="22"/>
       <c r="O52" s="22"/>
     </row>
-    <row r="53" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="53" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" s="22" t="s">
         <v>226</v>
       </c>
@@ -6771,7 +6775,7 @@
       <c r="N53" s="22"/>
       <c r="O53" s="22"/>
     </row>
-    <row r="54" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="54" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="22" t="s">
         <v>229</v>
       </c>
@@ -6800,7 +6804,7 @@
       <c r="N54" s="22"/>
       <c r="O54" s="22"/>
     </row>
-    <row r="55" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="55" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="22" t="s">
         <v>232</v>
       </c>
@@ -6831,7 +6835,7 @@
       <c r="N55" s="22"/>
       <c r="O55" s="22"/>
     </row>
-    <row r="56" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="56" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" s="22" t="s">
         <v>235</v>
       </c>
@@ -6864,7 +6868,7 @@
       <c r="N56" s="22"/>
       <c r="O56" s="22"/>
     </row>
-    <row r="57" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="57" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="22" t="s">
         <v>238</v>
       </c>
@@ -6897,7 +6901,7 @@
       <c r="N57" s="22"/>
       <c r="O57" s="22"/>
     </row>
-    <row r="58" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="58" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A58" s="22" t="s">
         <v>239</v>
       </c>
@@ -6928,7 +6932,7 @@
       <c r="N58" s="22"/>
       <c r="O58" s="22"/>
     </row>
-    <row r="59" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="59" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="22" t="s">
         <v>243</v>
       </c>
@@ -6961,7 +6965,7 @@
       <c r="N59" s="22"/>
       <c r="O59" s="22"/>
     </row>
-    <row r="60" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="60" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A60" s="22" t="s">
         <v>247</v>
       </c>
@@ -6996,7 +7000,7 @@
       <c r="N60" s="22"/>
       <c r="O60" s="22"/>
     </row>
-    <row r="61" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="61" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A61" s="22" t="s">
         <v>251</v>
       </c>
@@ -7025,7 +7029,7 @@
       <c r="N61" s="22"/>
       <c r="O61" s="22"/>
     </row>
-    <row r="62" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="62" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A62" s="22" t="s">
         <v>254</v>
       </c>
@@ -7058,7 +7062,7 @@
       <c r="N62" s="22"/>
       <c r="O62" s="22"/>
     </row>
-    <row r="63" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="63" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="22" t="s">
         <v>256</v>
       </c>
@@ -7089,7 +7093,7 @@
       <c r="N63" s="22"/>
       <c r="O63" s="22"/>
     </row>
-    <row r="64" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="64" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A64" s="22" t="s">
         <v>259</v>
       </c>
@@ -7122,7 +7126,7 @@
       <c r="N64" s="22"/>
       <c r="O64" s="22"/>
     </row>
-    <row r="65" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="65" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A65" s="22" t="s">
         <v>263</v>
       </c>
@@ -7151,7 +7155,7 @@
       <c r="N65" s="22"/>
       <c r="O65" s="22"/>
     </row>
-    <row r="66" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="66" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A66" s="22" t="s">
         <v>267</v>
       </c>
@@ -7184,7 +7188,7 @@
       <c r="N66" s="22"/>
       <c r="O66" s="22"/>
     </row>
-    <row r="67" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="67" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A67" s="22" t="s">
         <v>270</v>
       </c>
@@ -7219,7 +7223,7 @@
       <c r="N67" s="22"/>
       <c r="O67" s="22"/>
     </row>
-    <row r="68" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="68" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" s="22" t="s">
         <v>274</v>
       </c>
@@ -7254,7 +7258,7 @@
       <c r="N68" s="22"/>
       <c r="O68" s="22"/>
     </row>
-    <row r="69" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="69" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" s="22" t="s">
         <v>276</v>
       </c>
@@ -7285,7 +7289,7 @@
       <c r="N69" s="22"/>
       <c r="O69" s="22"/>
     </row>
-    <row r="70" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="70" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A70" s="22" t="s">
         <v>279</v>
       </c>
@@ -7318,7 +7322,7 @@
       <c r="N70" s="22"/>
       <c r="O70" s="22"/>
     </row>
-    <row r="71" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="71" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" s="22" t="s">
         <v>282</v>
       </c>
@@ -7349,7 +7353,7 @@
       <c r="N71" s="22"/>
       <c r="O71" s="22"/>
     </row>
-    <row r="72" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="72" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" s="22" t="s">
         <v>286</v>
       </c>
@@ -7378,7 +7382,7 @@
       <c r="N72" s="22"/>
       <c r="O72" s="22"/>
     </row>
-    <row r="73" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="73" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A73" s="22" t="s">
         <v>289</v>
       </c>
@@ -7411,7 +7415,7 @@
       <c r="N73" s="22"/>
       <c r="O73" s="22"/>
     </row>
-    <row r="74" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="74" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" s="22" t="s">
         <v>293</v>
       </c>
@@ -7440,7 +7444,7 @@
       <c r="N74" s="22"/>
       <c r="O74" s="22"/>
     </row>
-    <row r="75" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="75" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" s="22" t="s">
         <v>295</v>
       </c>
@@ -7471,7 +7475,7 @@
       <c r="N75" s="22"/>
       <c r="O75" s="22"/>
     </row>
-    <row r="76" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="76" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" s="22" t="s">
         <v>298</v>
       </c>
@@ -7504,7 +7508,7 @@
       <c r="N76" s="22"/>
       <c r="O76" s="22"/>
     </row>
-    <row r="77" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="77" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" s="22" t="s">
         <v>301</v>
       </c>
@@ -7539,7 +7543,7 @@
       <c r="N77" s="22"/>
       <c r="O77" s="22"/>
     </row>
-    <row r="78" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="78" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" s="22" t="s">
         <v>304</v>
       </c>
@@ -7576,7 +7580,7 @@
       <c r="N78" s="22"/>
       <c r="O78" s="22"/>
     </row>
-    <row r="79" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="79" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="22" t="s">
         <v>307</v>
       </c>
@@ -7605,7 +7609,7 @@
       <c r="N79" s="22"/>
       <c r="O79" s="22"/>
     </row>
-    <row r="80" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="80" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" s="22" t="s">
         <v>311</v>
       </c>
@@ -7642,7 +7646,7 @@
       <c r="N80" s="22"/>
       <c r="O80" s="22"/>
     </row>
-    <row r="81" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="81" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A81" s="22" t="s">
         <v>315</v>
       </c>
@@ -7677,7 +7681,7 @@
       <c r="N81" s="22"/>
       <c r="O81" s="22"/>
     </row>
-    <row r="82" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="82" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A82" s="22" t="s">
         <v>319</v>
       </c>
@@ -7708,7 +7712,7 @@
       <c r="N82" s="22"/>
       <c r="O82" s="22"/>
     </row>
-    <row r="83" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="83" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A83" s="22" t="s">
         <v>321</v>
       </c>
@@ -7739,7 +7743,7 @@
       <c r="N83" s="22"/>
       <c r="O83" s="22"/>
     </row>
-    <row r="84" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="84" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A84" s="22" t="s">
         <v>324</v>
       </c>
@@ -7774,7 +7778,7 @@
       <c r="N84" s="22"/>
       <c r="O84" s="22"/>
     </row>
-    <row r="85" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="85" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A85" s="22" t="s">
         <v>327</v>
       </c>
@@ -7805,7 +7809,7 @@
       <c r="N85" s="22"/>
       <c r="O85" s="22"/>
     </row>
-    <row r="86" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="86" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A86" s="22" t="s">
         <v>330</v>
       </c>
@@ -7838,7 +7842,7 @@
       <c r="N86" s="22"/>
       <c r="O86" s="22"/>
     </row>
-    <row r="87" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="87" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A87" s="22" t="s">
         <v>331</v>
       </c>
@@ -7869,7 +7873,7 @@
       <c r="N87" s="22"/>
       <c r="O87" s="22"/>
     </row>
-    <row r="88" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="88" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A88" s="22" t="s">
         <v>335</v>
       </c>
@@ -7902,7 +7906,7 @@
       <c r="N88" s="22"/>
       <c r="O88" s="22"/>
     </row>
-    <row r="89" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="89" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A89" s="22" t="s">
         <v>338</v>
       </c>
@@ -7937,7 +7941,7 @@
       <c r="N89" s="22"/>
       <c r="O89" s="22"/>
     </row>
-    <row r="90" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="90" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A90" s="22" t="s">
         <v>341</v>
       </c>
@@ -7972,7 +7976,7 @@
       <c r="N90" s="22"/>
       <c r="O90" s="22"/>
     </row>
-    <row r="91" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="91" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A91" s="22" t="s">
         <v>344</v>
       </c>
@@ -8001,7 +8005,7 @@
       <c r="N91" s="22"/>
       <c r="O91" s="22"/>
     </row>
-    <row r="92" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="92" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A92" s="22" t="s">
         <v>347</v>
       </c>
@@ -8034,7 +8038,7 @@
       <c r="N92" s="22"/>
       <c r="O92" s="22"/>
     </row>
-    <row r="93" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="93" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A93" s="22" t="s">
         <v>350</v>
       </c>
@@ -8067,7 +8071,7 @@
       <c r="N93" s="22"/>
       <c r="O93" s="22"/>
     </row>
-    <row r="94" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="94" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A94" s="22" t="s">
         <v>353</v>
       </c>
@@ -8096,7 +8100,7 @@
       <c r="N94" s="22"/>
       <c r="O94" s="22"/>
     </row>
-    <row r="95" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="95" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A95" s="22" t="s">
         <v>357</v>
       </c>
@@ -8127,7 +8131,7 @@
       <c r="N95" s="22"/>
       <c r="O95" s="22"/>
     </row>
-    <row r="96" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="96" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A96" s="22" t="s">
         <v>360</v>
       </c>
@@ -8156,7 +8160,7 @@
       <c r="N96" s="22"/>
       <c r="O96" s="22"/>
     </row>
-    <row r="97" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="97" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A97" s="22" t="s">
         <v>364</v>
       </c>
@@ -8187,7 +8191,7 @@
       <c r="N97" s="22"/>
       <c r="O97" s="22"/>
     </row>
-    <row r="98" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="98" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A98" s="22" t="s">
         <v>367</v>
       </c>
@@ -8218,7 +8222,7 @@
       <c r="N98" s="22"/>
       <c r="O98" s="22"/>
     </row>
-    <row r="99" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="99" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A99" s="22" t="s">
         <v>371</v>
       </c>
@@ -8249,7 +8253,7 @@
       <c r="N99" s="22"/>
       <c r="O99" s="22"/>
     </row>
-    <row r="100" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="100" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A100" s="22" t="s">
         <v>374</v>
       </c>
@@ -8278,7 +8282,7 @@
       <c r="N100" s="22"/>
       <c r="O100" s="22"/>
     </row>
-    <row r="101" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="101" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A101" s="22" t="s">
         <v>376</v>
       </c>
@@ -8309,7 +8313,7 @@
       <c r="N101" s="22"/>
       <c r="O101" s="22"/>
     </row>
-    <row r="102" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="102" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A102" s="22" t="s">
         <v>378</v>
       </c>
@@ -8338,7 +8342,7 @@
       <c r="N102" s="22"/>
       <c r="O102" s="22"/>
     </row>
-    <row r="103" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="103" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A103" s="22" t="s">
         <v>382</v>
       </c>
@@ -8369,7 +8373,7 @@
       <c r="N103" s="22"/>
       <c r="O103" s="22"/>
     </row>
-    <row r="104" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="104" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A104" s="22" t="s">
         <v>385</v>
       </c>
@@ -8404,7 +8408,7 @@
       <c r="N104" s="22"/>
       <c r="O104" s="22"/>
     </row>
-    <row r="105" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="105" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A105" s="22" t="s">
         <v>388</v>
       </c>
@@ -8435,7 +8439,7 @@
       <c r="N105" s="22"/>
       <c r="O105" s="22"/>
     </row>
-    <row r="106" spans="1:15" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="106" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A106" s="22" t="s">
         <v>391</v>
       </c>
@@ -8470,7 +8474,7 @@
       <c r="N106" s="22"/>
       <c r="O106" s="22"/>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A107" s="22" t="s">
         <v>394</v>
       </c>
@@ -8501,7 +8505,7 @@
       <c r="N107" s="22"/>
       <c r="O107" s="22"/>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A108" s="22" t="s">
         <v>397</v>
       </c>
@@ -8534,7 +8538,7 @@
       <c r="N108" s="22"/>
       <c r="O108" s="22"/>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A109" s="22" t="s">
         <v>400</v>
       </c>
@@ -8567,7 +8571,7 @@
       <c r="N109" s="22"/>
       <c r="O109" s="22"/>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A110" s="22" t="s">
         <v>403</v>
       </c>
@@ -8598,7 +8602,7 @@
       <c r="N110" s="22"/>
       <c r="O110" s="22"/>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A111" s="22" t="s">
         <v>406</v>
       </c>
@@ -8633,7 +8637,7 @@
       <c r="N111" s="22"/>
       <c r="O111" s="22"/>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A112" s="22" t="s">
         <v>409</v>
       </c>
@@ -8666,7 +8670,7 @@
       <c r="N112" s="22"/>
       <c r="O112" s="22"/>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A113" s="22" t="s">
         <v>412</v>
       </c>
@@ -8701,7 +8705,7 @@
       <c r="N113" s="22"/>
       <c r="O113" s="22"/>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A114" s="22" t="s">
         <v>415</v>
       </c>
@@ -8734,7 +8738,7 @@
       <c r="N114" s="22"/>
       <c r="O114" s="22"/>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A115" s="22" t="s">
         <v>418</v>
       </c>
@@ -8771,7 +8775,7 @@
       <c r="N115" s="22"/>
       <c r="O115" s="22"/>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A116" s="22" t="s">
         <v>421</v>
       </c>
@@ -8806,7 +8810,7 @@
       <c r="N116" s="22"/>
       <c r="O116" s="22"/>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A117" s="22" t="s">
         <v>424</v>
       </c>
@@ -8843,7 +8847,7 @@
       <c r="N117" s="22"/>
       <c r="O117" s="22"/>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A118" s="22" t="s">
         <v>427</v>
       </c>
@@ -8876,7 +8880,7 @@
       <c r="N118" s="22"/>
       <c r="O118" s="22"/>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A119" s="22" t="s">
         <v>430</v>
       </c>
@@ -8907,7 +8911,7 @@
       <c r="N119" s="22"/>
       <c r="O119" s="22"/>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A120" s="22" t="s">
         <v>433</v>
       </c>
@@ -8936,7 +8940,7 @@
       <c r="N120" s="22"/>
       <c r="O120" s="22"/>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A121" s="22" t="s">
         <v>436</v>
       </c>
@@ -8969,7 +8973,7 @@
       <c r="N121" s="22"/>
       <c r="O121" s="22"/>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A122" s="22" t="s">
         <v>439</v>
       </c>
@@ -9002,7 +9006,7 @@
       <c r="N122" s="22"/>
       <c r="O122" s="22"/>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A123" s="22" t="s">
         <v>442</v>
       </c>
@@ -9035,7 +9039,7 @@
       <c r="N123" s="22"/>
       <c r="O123" s="22"/>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A124" s="22" t="s">
         <v>445</v>
       </c>
@@ -9064,7 +9068,7 @@
       <c r="N124" s="22"/>
       <c r="O124" s="22"/>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="125" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A125" s="22" t="s">
         <v>448</v>
       </c>
@@ -9095,7 +9099,7 @@
       <c r="N125" s="22"/>
       <c r="O125" s="22"/>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="126" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A126" s="22" t="s">
         <v>451</v>
       </c>
@@ -9128,7 +9132,7 @@
       <c r="N126" s="22"/>
       <c r="O126" s="22"/>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A127" s="22" t="s">
         <v>454</v>
       </c>
@@ -9157,7 +9161,7 @@
       <c r="N127" s="22"/>
       <c r="O127" s="22"/>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A128" s="22" t="s">
         <v>456</v>
       </c>
@@ -9192,7 +9196,7 @@
       <c r="N128" s="22"/>
       <c r="O128" s="22"/>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="129" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A129" s="22" t="s">
         <v>459</v>
       </c>
@@ -9227,7 +9231,7 @@
       <c r="N129" s="22"/>
       <c r="O129" s="22"/>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="130" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A130" s="22" t="s">
         <v>461</v>
       </c>
@@ -9260,7 +9264,7 @@
       <c r="N130" s="22"/>
       <c r="O130" s="22"/>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A131" s="22" t="s">
         <v>464</v>
       </c>
@@ -9291,7 +9295,7 @@
       <c r="N131" s="22"/>
       <c r="O131" s="22"/>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="132" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A132" s="22" t="s">
         <v>467</v>
       </c>
@@ -9324,7 +9328,7 @@
       <c r="N132" s="22"/>
       <c r="O132" s="22"/>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="133" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A133" s="22" t="s">
         <v>470</v>
       </c>
@@ -9361,7 +9365,7 @@
       <c r="N133" s="22"/>
       <c r="O133" s="22"/>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="134" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A134" s="22" t="s">
         <v>473</v>
       </c>
@@ -9390,7 +9394,7 @@
       <c r="N134" s="22"/>
       <c r="O134" s="22"/>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="135" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A135" s="22" t="s">
         <v>475</v>
       </c>
@@ -9421,7 +9425,7 @@
       <c r="N135" s="22"/>
       <c r="O135" s="22"/>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="136" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A136" s="22" t="s">
         <v>478</v>
       </c>
@@ -9452,7 +9456,7 @@
       <c r="N136" s="22"/>
       <c r="O136" s="22"/>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="137" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A137" s="22" t="s">
         <v>481</v>
       </c>
@@ -9485,7 +9489,7 @@
       <c r="N137" s="22"/>
       <c r="O137" s="22"/>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="138" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A138" s="22" t="s">
         <v>484</v>
       </c>
@@ -9516,7 +9520,7 @@
       <c r="N138" s="22"/>
       <c r="O138" s="22"/>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="139" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A139" s="22" t="s">
         <v>487</v>
       </c>
@@ -9547,7 +9551,7 @@
       <c r="N139" s="22"/>
       <c r="O139" s="22"/>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="140" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A140" s="22" t="s">
         <v>490</v>
       </c>
@@ -9580,7 +9584,7 @@
       <c r="N140" s="22"/>
       <c r="O140" s="22"/>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="141" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A141" s="22" t="s">
         <v>493</v>
       </c>
@@ -9611,7 +9615,7 @@
       <c r="N141" s="22"/>
       <c r="O141" s="22"/>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="142" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A142" s="22" t="s">
         <v>496</v>
       </c>
@@ -9648,7 +9652,7 @@
       <c r="N142" s="22"/>
       <c r="O142" s="22"/>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="143" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A143" s="22" t="s">
         <v>499</v>
       </c>
@@ -9677,7 +9681,7 @@
       <c r="N143" s="22"/>
       <c r="O143" s="22"/>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="144" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A144" s="22" t="s">
         <v>501</v>
       </c>
@@ -9708,7 +9712,7 @@
       <c r="N144" s="22"/>
       <c r="O144" s="22"/>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="145" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A145" s="22" t="s">
         <v>504</v>
       </c>
@@ -9737,7 +9741,7 @@
       <c r="N145" s="22"/>
       <c r="O145" s="22"/>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="146" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A146" s="22" t="s">
         <v>507</v>
       </c>
@@ -9766,7 +9770,7 @@
       <c r="N146" s="22"/>
       <c r="O146" s="22"/>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="147" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A147" s="22" t="s">
         <v>510</v>
       </c>
@@ -9801,7 +9805,7 @@
       <c r="N147" s="22"/>
       <c r="O147" s="22"/>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="148" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A148" s="22" t="s">
         <v>512</v>
       </c>
@@ -9834,7 +9838,7 @@
       <c r="N148" s="22"/>
       <c r="O148" s="22"/>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="149" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A149" s="22" t="s">
         <v>515</v>
       </c>
@@ -9863,7 +9867,7 @@
       <c r="N149" s="22"/>
       <c r="O149" s="22"/>
     </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="150" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A150" s="22" t="s">
         <v>518</v>
       </c>
@@ -9894,7 +9898,7 @@
       <c r="N150" s="22"/>
       <c r="O150" s="22"/>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="151" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A151" s="22" t="s">
         <v>521</v>
       </c>
@@ -9925,7 +9929,7 @@
       <c r="N151" s="22"/>
       <c r="O151" s="22"/>
     </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="152" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A152" s="22" t="s">
         <v>524</v>
       </c>
@@ -9958,7 +9962,7 @@
       <c r="N152" s="22"/>
       <c r="O152" s="22"/>
     </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="153" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A153" s="22" t="s">
         <v>526</v>
       </c>
@@ -9991,7 +9995,7 @@
       <c r="N153" s="22"/>
       <c r="O153" s="22"/>
     </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="154" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A154" s="22" t="s">
         <v>529</v>
       </c>
@@ -10020,7 +10024,7 @@
       <c r="N154" s="22"/>
       <c r="O154" s="22"/>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="155" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A155" s="22" t="s">
         <v>532</v>
       </c>
@@ -10053,7 +10057,7 @@
       <c r="N155" s="22"/>
       <c r="O155" s="22"/>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="156" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A156" s="22" t="s">
         <v>535</v>
       </c>
@@ -10086,7 +10090,7 @@
       <c r="N156" s="22"/>
       <c r="O156" s="22"/>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="157" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A157" s="22" t="s">
         <v>538</v>
       </c>
@@ -10117,7 +10121,7 @@
       <c r="N157" s="22"/>
       <c r="O157" s="22"/>
     </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="158" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A158" s="22" t="s">
         <v>540</v>
       </c>
@@ -10150,7 +10154,7 @@
       <c r="N158" s="22"/>
       <c r="O158" s="22"/>
     </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="159" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A159" s="22" t="s">
         <v>543</v>
       </c>
@@ -10185,7 +10189,7 @@
       <c r="N159" s="22"/>
       <c r="O159" s="22"/>
     </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="160" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A160" s="22" t="s">
         <v>546</v>
       </c>
@@ -10216,7 +10220,7 @@
       <c r="N160" s="22"/>
       <c r="O160" s="22"/>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="161" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A161" s="22" t="s">
         <v>549</v>
       </c>
@@ -10247,7 +10251,7 @@
       <c r="N161" s="22"/>
       <c r="O161" s="22"/>
     </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="162" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A162" s="22" t="s">
         <v>552</v>
       </c>
@@ -10276,7 +10280,7 @@
       <c r="N162" s="22"/>
       <c r="O162" s="22"/>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="163" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A163" s="22" t="s">
         <v>554</v>
       </c>
@@ -10307,7 +10311,7 @@
       <c r="N163" s="22"/>
       <c r="O163" s="22"/>
     </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="164" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A164" s="22" t="s">
         <v>557</v>
       </c>
@@ -10342,7 +10346,7 @@
       <c r="N164" s="22"/>
       <c r="O164" s="22"/>
     </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="165" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A165" s="22" t="s">
         <v>560</v>
       </c>
@@ -10371,7 +10375,7 @@
       <c r="N165" s="22"/>
       <c r="O165" s="22"/>
     </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="166" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A166" s="22" t="s">
         <v>562</v>
       </c>
@@ -10406,7 +10410,7 @@
       <c r="N166" s="22"/>
       <c r="O166" s="22"/>
     </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="167" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A167" s="22" t="s">
         <v>564</v>
       </c>
@@ -10437,7 +10441,7 @@
       <c r="N167" s="22"/>
       <c r="O167" s="22"/>
     </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="168" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A168" s="22" t="s">
         <v>566</v>
       </c>
@@ -10468,7 +10472,7 @@
       <c r="N168" s="22"/>
       <c r="O168" s="22"/>
     </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="169" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A169" s="22" t="s">
         <v>568</v>
       </c>
@@ -10501,7 +10505,7 @@
       <c r="N169" s="22"/>
       <c r="O169" s="22"/>
     </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="170" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A170" s="22" t="s">
         <v>571</v>
       </c>
@@ -10536,7 +10540,7 @@
       <c r="N170" s="22"/>
       <c r="O170" s="22"/>
     </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="171" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A171" s="22" t="s">
         <v>573</v>
       </c>
@@ -10569,7 +10573,7 @@
       <c r="N171" s="22"/>
       <c r="O171" s="22"/>
     </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="172" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A172" s="22" t="s">
         <v>576</v>
       </c>
@@ -10598,7 +10602,7 @@
       <c r="N172" s="22"/>
       <c r="O172" s="22"/>
     </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="173" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A173" s="22" t="s">
         <v>578</v>
       </c>
@@ -10627,7 +10631,7 @@
       <c r="N173" s="22"/>
       <c r="O173" s="22"/>
     </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="174" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A174" s="22" t="s">
         <v>581</v>
       </c>
@@ -10660,7 +10664,7 @@
       <c r="N174" s="22"/>
       <c r="O174" s="22"/>
     </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="175" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A175" s="22" t="s">
         <v>584</v>
       </c>
@@ -10691,7 +10695,7 @@
       <c r="N175" s="22"/>
       <c r="O175" s="22"/>
     </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="176" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A176" s="22" t="s">
         <v>587</v>
       </c>
@@ -10722,7 +10726,7 @@
       <c r="N176" s="22"/>
       <c r="O176" s="22"/>
     </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="177" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A177" s="22" t="s">
         <v>590</v>
       </c>
@@ -10759,7 +10763,7 @@
       <c r="N177" s="22"/>
       <c r="O177" s="22"/>
     </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="178" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A178" s="22" t="s">
         <v>592</v>
       </c>
@@ -10790,7 +10794,7 @@
       <c r="N178" s="22"/>
       <c r="O178" s="22"/>
     </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="179" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A179" s="22" t="s">
         <v>594</v>
       </c>
@@ -10823,7 +10827,7 @@
       <c r="N179" s="22"/>
       <c r="O179" s="22"/>
     </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="180" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A180" s="22" t="s">
         <v>597</v>
       </c>
@@ -10854,7 +10858,7 @@
       <c r="N180" s="22"/>
       <c r="O180" s="22"/>
     </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="181" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A181" s="22" t="s">
         <v>599</v>
       </c>
@@ -10885,7 +10889,7 @@
       <c r="N181" s="22"/>
       <c r="O181" s="22"/>
     </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="182" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A182" s="22" t="s">
         <v>602</v>
       </c>
@@ -10918,7 +10922,7 @@
       <c r="N182" s="22"/>
       <c r="O182" s="22"/>
     </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="183" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A183" s="22" t="s">
         <v>604</v>
       </c>
@@ -10955,7 +10959,7 @@
       <c r="N183" s="22"/>
       <c r="O183" s="22"/>
     </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="184" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A184" s="22" t="s">
         <v>606</v>
       </c>
@@ -10986,7 +10990,7 @@
       <c r="N184" s="22"/>
       <c r="O184" s="22"/>
     </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="185" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A185" s="22" t="s">
         <v>608</v>
       </c>
@@ -11019,7 +11023,7 @@
       <c r="N185" s="22"/>
       <c r="O185" s="22"/>
     </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="186" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A186" s="22" t="s">
         <v>611</v>
       </c>
@@ -11052,7 +11056,7 @@
       <c r="N186" s="22"/>
       <c r="O186" s="22"/>
     </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="187" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A187" s="22" t="s">
         <v>613</v>
       </c>
@@ -11085,7 +11089,7 @@
       <c r="N187" s="22"/>
       <c r="O187" s="22"/>
     </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="188" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A188" s="22" t="s">
         <v>616</v>
       </c>
@@ -11116,7 +11120,7 @@
       <c r="N188" s="22"/>
       <c r="O188" s="22"/>
     </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="189" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A189" s="22" t="s">
         <v>619</v>
       </c>
@@ -11147,7 +11151,7 @@
       <c r="N189" s="22"/>
       <c r="O189" s="22"/>
     </row>
-    <row r="190" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="190" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A190" s="22" t="s">
         <v>622</v>
       </c>
@@ -11180,7 +11184,7 @@
       <c r="N190" s="22"/>
       <c r="O190" s="22"/>
     </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="191" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A191" s="22" t="s">
         <v>624</v>
       </c>
@@ -11209,7 +11213,7 @@
       <c r="N191" s="22"/>
       <c r="O191" s="22"/>
     </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="192" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A192" s="22" t="s">
         <v>627</v>
       </c>
@@ -11240,7 +11244,7 @@
       <c r="N192" s="22"/>
       <c r="O192" s="22"/>
     </row>
-    <row r="193" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="193" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A193" s="22" t="s">
         <v>630</v>
       </c>
@@ -11271,7 +11275,7 @@
       <c r="N193" s="22"/>
       <c r="O193" s="22"/>
     </row>
-    <row r="194" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="194" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A194" s="22" t="s">
         <v>632</v>
       </c>
@@ -11302,7 +11306,7 @@
       <c r="N194" s="22"/>
       <c r="O194" s="22"/>
     </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="195" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A195" s="22" t="s">
         <v>635</v>
       </c>
@@ -11331,7 +11335,7 @@
       <c r="N195" s="22"/>
       <c r="O195" s="22"/>
     </row>
-    <row r="196" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="196" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A196" s="22" t="s">
         <v>638</v>
       </c>
@@ -11364,7 +11368,7 @@
       <c r="N196" s="22"/>
       <c r="O196" s="22"/>
     </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="197" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A197" s="22" t="s">
         <v>640</v>
       </c>
@@ -11397,7 +11401,7 @@
       <c r="N197" s="22"/>
       <c r="O197" s="22"/>
     </row>
-    <row r="198" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="198" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A198" s="22" t="s">
         <v>643</v>
       </c>
@@ -11430,7 +11434,7 @@
       <c r="N198" s="22"/>
       <c r="O198" s="22"/>
     </row>
-    <row r="199" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="199" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A199" s="22" t="s">
         <v>646</v>
       </c>
@@ -11463,7 +11467,7 @@
       <c r="N199" s="22"/>
       <c r="O199" s="22"/>
     </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="200" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A200" s="22" t="s">
         <v>649</v>
       </c>
@@ -11492,7 +11496,7 @@
       <c r="N200" s="22"/>
       <c r="O200" s="22"/>
     </row>
-    <row r="201" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="201" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A201" s="22" t="s">
         <v>652</v>
       </c>
@@ -11525,7 +11529,7 @@
       <c r="N201" s="22"/>
       <c r="O201" s="22"/>
     </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="202" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A202" s="22" t="s">
         <v>654</v>
       </c>
@@ -11558,7 +11562,7 @@
       <c r="N202" s="22"/>
       <c r="O202" s="22"/>
     </row>
-    <row r="203" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="203" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A203" s="22" t="s">
         <v>657</v>
       </c>
@@ -11593,7 +11597,7 @@
       <c r="N203" s="22"/>
       <c r="O203" s="22"/>
     </row>
-    <row r="204" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="204" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A204" s="22" t="s">
         <v>659</v>
       </c>
@@ -11626,7 +11630,7 @@
       <c r="N204" s="22"/>
       <c r="O204" s="22"/>
     </row>
-    <row r="205" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="205" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A205" s="22" t="s">
         <v>662</v>
       </c>
@@ -11657,7 +11661,7 @@
       <c r="N205" s="22"/>
       <c r="O205" s="22"/>
     </row>
-    <row r="206" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="206" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A206" s="22" t="s">
         <v>664</v>
       </c>
@@ -11690,7 +11694,7 @@
       <c r="N206" s="22"/>
       <c r="O206" s="22"/>
     </row>
-    <row r="207" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="207" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A207" s="22" t="s">
         <v>667</v>
       </c>
@@ -11723,7 +11727,7 @@
       <c r="N207" s="22"/>
       <c r="O207" s="22"/>
     </row>
-    <row r="208" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="208" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A208" s="22" t="s">
         <v>669</v>
       </c>
@@ -11754,7 +11758,7 @@
       <c r="N208" s="22"/>
       <c r="O208" s="22"/>
     </row>
-    <row r="209" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="209" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A209" s="22" t="s">
         <v>672</v>
       </c>
@@ -11785,7 +11789,7 @@
       <c r="N209" s="22"/>
       <c r="O209" s="22"/>
     </row>
-    <row r="210" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="210" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A210" s="22" t="s">
         <v>674</v>
       </c>
@@ -11814,7 +11818,7 @@
       <c r="N210" s="22"/>
       <c r="O210" s="22"/>
     </row>
-    <row r="211" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="211" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A211" s="22" t="s">
         <v>677</v>
       </c>
@@ -11849,7 +11853,7 @@
       <c r="N211" s="22"/>
       <c r="O211" s="22"/>
     </row>
-    <row r="212" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="212" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A212" s="22" t="s">
         <v>679</v>
       </c>
@@ -11880,7 +11884,7 @@
       <c r="N212" s="22"/>
       <c r="O212" s="22"/>
     </row>
-    <row r="213" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="213" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A213" s="22" t="s">
         <v>682</v>
       </c>
@@ -11911,7 +11915,7 @@
       <c r="N213" s="22"/>
       <c r="O213" s="22"/>
     </row>
-    <row r="214" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="214" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A214" s="22" t="s">
         <v>684</v>
       </c>
@@ -11946,7 +11950,7 @@
       <c r="N214" s="22"/>
       <c r="O214" s="22"/>
     </row>
-    <row r="215" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="215" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A215" s="22" t="s">
         <v>687</v>
       </c>
@@ -11977,7 +11981,7 @@
       <c r="N215" s="22"/>
       <c r="O215" s="22"/>
     </row>
-    <row r="216" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="216" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A216" s="22" t="s">
         <v>689</v>
       </c>
@@ -12010,7 +12014,7 @@
       <c r="N216" s="22"/>
       <c r="O216" s="22"/>
     </row>
-    <row r="217" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="217" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A217" s="22" t="s">
         <v>692</v>
       </c>
@@ -12043,7 +12047,7 @@
       <c r="N217" s="22"/>
       <c r="O217" s="22"/>
     </row>
-    <row r="218" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="218" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A218" s="22" t="s">
         <v>695</v>
       </c>
@@ -12072,7 +12076,7 @@
       <c r="N218" s="22"/>
       <c r="O218" s="22"/>
     </row>
-    <row r="219" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="219" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A219" s="22" t="s">
         <v>698</v>
       </c>
@@ -12101,7 +12105,7 @@
       <c r="N219" s="22"/>
       <c r="O219" s="22"/>
     </row>
-    <row r="220" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="220" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A220" s="22" t="s">
         <v>701</v>
       </c>
@@ -12130,7 +12134,7 @@
       <c r="N220" s="22"/>
       <c r="O220" s="22"/>
     </row>
-    <row r="221" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="221" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A221" s="22" t="s">
         <v>704</v>
       </c>
@@ -12161,7 +12165,7 @@
       <c r="N221" s="22"/>
       <c r="O221" s="22"/>
     </row>
-    <row r="222" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="222" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A222" s="22" t="s">
         <v>706</v>
       </c>
@@ -12190,7 +12194,7 @@
       <c r="N222" s="22"/>
       <c r="O222" s="22"/>
     </row>
-    <row r="223" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="223" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A223" s="22" t="s">
         <v>708</v>
       </c>
@@ -12223,7 +12227,7 @@
       <c r="N223" s="22"/>
       <c r="O223" s="22"/>
     </row>
-    <row r="224" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="224" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A224" s="22" t="s">
         <v>711</v>
       </c>
@@ -12258,7 +12262,7 @@
       <c r="N224" s="22"/>
       <c r="O224" s="22"/>
     </row>
-    <row r="225" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="225" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A225" s="22" t="s">
         <v>713</v>
       </c>
@@ -12289,7 +12293,7 @@
       <c r="N225" s="22"/>
       <c r="O225" s="22"/>
     </row>
-    <row r="226" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="226" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A226" s="22" t="s">
         <v>716</v>
       </c>
@@ -12322,7 +12326,7 @@
       <c r="N226" s="22"/>
       <c r="O226" s="22"/>
     </row>
-    <row r="227" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="227" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A227" s="22" t="s">
         <v>719</v>
       </c>
@@ -12353,7 +12357,7 @@
       <c r="N227" s="22"/>
       <c r="O227" s="22"/>
     </row>
-    <row r="228" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="228" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A228" s="22" t="s">
         <v>722</v>
       </c>
@@ -12384,7 +12388,7 @@
       <c r="N228" s="22"/>
       <c r="O228" s="22"/>
     </row>
-    <row r="229" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="229" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A229" s="22" t="s">
         <v>724</v>
       </c>
@@ -12413,7 +12417,7 @@
       <c r="N229" s="22"/>
       <c r="O229" s="22"/>
     </row>
-    <row r="230" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="230" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A230" s="22" t="s">
         <v>727</v>
       </c>
@@ -12446,7 +12450,7 @@
       <c r="N230" s="22"/>
       <c r="O230" s="22"/>
     </row>
-    <row r="231" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="231" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A231" s="22" t="s">
         <v>729</v>
       </c>
@@ -12475,7 +12479,7 @@
       <c r="N231" s="22"/>
       <c r="O231" s="22"/>
     </row>
-    <row r="232" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="232" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A232" s="22" t="s">
         <v>732</v>
       </c>
@@ -12504,7 +12508,7 @@
       <c r="N232" s="22"/>
       <c r="O232" s="22"/>
     </row>
-    <row r="233" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="233" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A233" s="22" t="s">
         <v>735</v>
       </c>
@@ -12535,7 +12539,7 @@
       <c r="N233" s="22"/>
       <c r="O233" s="22"/>
     </row>
-    <row r="234" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="234" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A234" s="22" t="s">
         <v>738</v>
       </c>
@@ -12566,7 +12570,7 @@
       <c r="N234" s="22"/>
       <c r="O234" s="22"/>
     </row>
-    <row r="235" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="235" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A235" s="22" t="s">
         <v>740</v>
       </c>
@@ -12597,7 +12601,7 @@
       <c r="N235" s="22"/>
       <c r="O235" s="22"/>
     </row>
-    <row r="236" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="236" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A236" s="22" t="s">
         <v>743</v>
       </c>
@@ -12632,7 +12636,7 @@
       <c r="N236" s="22"/>
       <c r="O236" s="22"/>
     </row>
-    <row r="237" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="237" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A237" s="22" t="s">
         <v>745</v>
       </c>
@@ -12667,7 +12671,7 @@
       <c r="N237" s="22"/>
       <c r="O237" s="22"/>
     </row>
-    <row r="238" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="238" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A238" s="22" t="s">
         <v>748</v>
       </c>
@@ -12696,7 +12700,7 @@
       <c r="N238" s="22"/>
       <c r="O238" s="22"/>
     </row>
-    <row r="239" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="239" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A239" s="22" t="s">
         <v>751</v>
       </c>
@@ -12729,7 +12733,7 @@
       <c r="N239" s="22"/>
       <c r="O239" s="22"/>
     </row>
-    <row r="240" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="240" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A240" s="22" t="s">
         <v>753</v>
       </c>
@@ -12764,7 +12768,7 @@
       <c r="N240" s="22"/>
       <c r="O240" s="22"/>
     </row>
-    <row r="241" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="241" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A241" s="22" t="s">
         <v>755</v>
       </c>
@@ -12797,7 +12801,7 @@
       <c r="N241" s="22"/>
       <c r="O241" s="22"/>
     </row>
-    <row r="242" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="242" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A242" s="22" t="s">
         <v>758</v>
       </c>
@@ -12830,7 +12834,7 @@
       <c r="N242" s="22"/>
       <c r="O242" s="22"/>
     </row>
-    <row r="243" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="243" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A243" s="22" t="s">
         <v>760</v>
       </c>
@@ -12861,7 +12865,7 @@
       <c r="N243" s="22"/>
       <c r="O243" s="22"/>
     </row>
-    <row r="244" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="244" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A244" s="22" t="s">
         <v>762</v>
       </c>
@@ -12894,7 +12898,7 @@
       <c r="N244" s="22"/>
       <c r="O244" s="22"/>
     </row>
-    <row r="245" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="245" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A245" s="22" t="s">
         <v>765</v>
       </c>
@@ -12929,7 +12933,7 @@
       <c r="N245" s="22"/>
       <c r="O245" s="22"/>
     </row>
-    <row r="246" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="246" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A246" s="22" t="s">
         <v>767</v>
       </c>
@@ -12962,7 +12966,7 @@
       <c r="N246" s="22"/>
       <c r="O246" s="22"/>
     </row>
-    <row r="247" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="247" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A247" s="22" t="s">
         <v>769</v>
       </c>
@@ -12993,7 +12997,7 @@
       <c r="N247" s="22"/>
       <c r="O247" s="22"/>
     </row>
-    <row r="248" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="248" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A248" s="22" t="s">
         <v>771</v>
       </c>
@@ -13026,7 +13030,7 @@
       <c r="N248" s="22"/>
       <c r="O248" s="22"/>
     </row>
-    <row r="249" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="249" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A249" s="22" t="s">
         <v>774</v>
       </c>
@@ -13059,7 +13063,7 @@
       <c r="N249" s="22"/>
       <c r="O249" s="22"/>
     </row>
-    <row r="250" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="250" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A250" s="22" t="s">
         <v>777</v>
       </c>
@@ -13094,7 +13098,7 @@
       <c r="N250" s="22"/>
       <c r="O250" s="22"/>
     </row>
-    <row r="251" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="251" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A251" s="22" t="s">
         <v>780</v>
       </c>
@@ -13129,7 +13133,7 @@
       <c r="N251" s="22"/>
       <c r="O251" s="22"/>
     </row>
-    <row r="252" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="252" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A252" s="22" t="s">
         <v>783</v>
       </c>
@@ -13162,7 +13166,7 @@
       <c r="N252" s="22"/>
       <c r="O252" s="22"/>
     </row>
-    <row r="253" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="253" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A253" s="22" t="s">
         <v>786</v>
       </c>
@@ -13193,7 +13197,7 @@
       <c r="N253" s="22"/>
       <c r="O253" s="22"/>
     </row>
-    <row r="254" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="254" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A254" s="22" t="s">
         <v>788</v>
       </c>
@@ -13224,7 +13228,7 @@
       <c r="N254" s="22"/>
       <c r="O254" s="22"/>
     </row>
-    <row r="255" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="255" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A255" s="22" t="s">
         <v>790</v>
       </c>
@@ -13253,7 +13257,7 @@
       <c r="N255" s="22"/>
       <c r="O255" s="22"/>
     </row>
-    <row r="256" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="256" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A256" s="22" t="s">
         <v>792</v>
       </c>
@@ -13284,7 +13288,7 @@
       <c r="N256" s="22"/>
       <c r="O256" s="22"/>
     </row>
-    <row r="257" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="257" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A257" s="22" t="s">
         <v>795</v>
       </c>
@@ -13315,7 +13319,7 @@
       <c r="N257" s="22"/>
       <c r="O257" s="22"/>
     </row>
-    <row r="258" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="258" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A258" s="22" t="s">
         <v>798</v>
       </c>
@@ -13350,7 +13354,7 @@
       <c r="N258" s="22"/>
       <c r="O258" s="22"/>
     </row>
-    <row r="259" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="259" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A259" s="22" t="s">
         <v>801</v>
       </c>
@@ -13379,7 +13383,7 @@
       <c r="N259" s="22"/>
       <c r="O259" s="22"/>
     </row>
-    <row r="260" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="260" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A260" s="22" t="s">
         <v>804</v>
       </c>
@@ -13408,7 +13412,7 @@
       <c r="N260" s="22"/>
       <c r="O260" s="22"/>
     </row>
-    <row r="261" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="261" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A261" s="22" t="s">
         <v>807</v>
       </c>
@@ -13439,7 +13443,7 @@
       <c r="N261" s="22"/>
       <c r="O261" s="22"/>
     </row>
-    <row r="262" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="262" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A262" s="22" t="s">
         <v>809</v>
       </c>
@@ -13474,7 +13478,7 @@
       <c r="N262" s="22"/>
       <c r="O262" s="22"/>
     </row>
-    <row r="263" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="263" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A263" s="22" t="s">
         <v>811</v>
       </c>
@@ -13507,7 +13511,7 @@
       <c r="N263" s="22"/>
       <c r="O263" s="22"/>
     </row>
-    <row r="264" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="264" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A264" s="22" t="s">
         <v>814</v>
       </c>
@@ -13540,7 +13544,7 @@
       <c r="N264" s="22"/>
       <c r="O264" s="22"/>
     </row>
-    <row r="265" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="265" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A265" s="22" t="s">
         <v>816</v>
       </c>
@@ -13569,7 +13573,7 @@
       <c r="N265" s="22"/>
       <c r="O265" s="22"/>
     </row>
-    <row r="266" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="266" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A266" s="22" t="s">
         <v>818</v>
       </c>
@@ -13602,7 +13606,7 @@
       <c r="N266" s="22"/>
       <c r="O266" s="22"/>
     </row>
-    <row r="267" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="267" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A267" s="22" t="s">
         <v>820</v>
       </c>
@@ -13637,7 +13641,7 @@
       <c r="N267" s="22"/>
       <c r="O267" s="22"/>
     </row>
-    <row r="268" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="268" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A268" s="22" t="s">
         <v>823</v>
       </c>
@@ -13670,7 +13674,7 @@
       <c r="N268" s="22"/>
       <c r="O268" s="22"/>
     </row>
-    <row r="269" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="269" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A269" s="22" t="s">
         <v>826</v>
       </c>
@@ -13705,7 +13709,7 @@
       <c r="N269" s="22"/>
       <c r="O269" s="22"/>
     </row>
-    <row r="270" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="270" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A270" s="22" t="s">
         <v>828</v>
       </c>
@@ -13740,7 +13744,7 @@
       <c r="N270" s="22"/>
       <c r="O270" s="22"/>
     </row>
-    <row r="271" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="271" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A271" s="22" t="s">
         <v>831</v>
       </c>
@@ -13773,7 +13777,7 @@
       <c r="N271" s="22"/>
       <c r="O271" s="22"/>
     </row>
-    <row r="272" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="272" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A272" s="22" t="s">
         <v>833</v>
       </c>
@@ -13804,7 +13808,7 @@
       <c r="N272" s="22"/>
       <c r="O272" s="22"/>
     </row>
-    <row r="273" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="273" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A273" s="22" t="s">
         <v>836</v>
       </c>
@@ -13833,7 +13837,7 @@
       <c r="N273" s="22"/>
       <c r="O273" s="22"/>
     </row>
-    <row r="274" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="274" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A274" s="22" t="s">
         <v>838</v>
       </c>
@@ -13864,7 +13868,7 @@
       <c r="N274" s="22"/>
       <c r="O274" s="22"/>
     </row>
-    <row r="275" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="275" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A275" s="22" t="s">
         <v>840</v>
       </c>
@@ -13899,7 +13903,7 @@
       <c r="N275" s="22"/>
       <c r="O275" s="22"/>
     </row>
-    <row r="276" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="276" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A276" s="22" t="s">
         <v>842</v>
       </c>
@@ -13930,7 +13934,7 @@
       <c r="N276" s="22"/>
       <c r="O276" s="22"/>
     </row>
-    <row r="277" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="277" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A277" s="22" t="s">
         <v>844</v>
       </c>
@@ -13961,7 +13965,7 @@
       <c r="N277" s="22"/>
       <c r="O277" s="22"/>
     </row>
-    <row r="278" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="278" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A278" s="22" t="s">
         <v>846</v>
       </c>
@@ -13994,7 +13998,7 @@
       <c r="N278" s="22"/>
       <c r="O278" s="22"/>
     </row>
-    <row r="279" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="279" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A279" s="22" t="s">
         <v>848</v>
       </c>
@@ -14023,7 +14027,7 @@
       <c r="N279" s="22"/>
       <c r="O279" s="22"/>
     </row>
-    <row r="280" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="280" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A280" s="22" t="s">
         <v>851</v>
       </c>
@@ -14060,7 +14064,7 @@
       <c r="N280" s="22"/>
       <c r="O280" s="22"/>
     </row>
-    <row r="281" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="281" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A281" s="22" t="s">
         <v>853</v>
       </c>
@@ -14095,7 +14099,7 @@
       <c r="N281" s="22"/>
       <c r="O281" s="22"/>
     </row>
-    <row r="282" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="282" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A282" s="22" t="s">
         <v>856</v>
       </c>
@@ -14124,7 +14128,7 @@
       <c r="N282" s="22"/>
       <c r="O282" s="22"/>
     </row>
-    <row r="283" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="283" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A283" s="22" t="s">
         <v>859</v>
       </c>
@@ -14155,7 +14159,7 @@
       <c r="N283" s="22"/>
       <c r="O283" s="22"/>
     </row>
-    <row r="284" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="284" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A284" s="22" t="s">
         <v>861</v>
       </c>
@@ -14184,7 +14188,7 @@
       <c r="N284" s="22"/>
       <c r="O284" s="22"/>
     </row>
-    <row r="285" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="285" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A285" s="22" t="s">
         <v>864</v>
       </c>
@@ -14217,7 +14221,7 @@
       <c r="N285" s="22"/>
       <c r="O285" s="22"/>
     </row>
-    <row r="286" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="286" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A286" s="22" t="s">
         <v>866</v>
       </c>
@@ -14246,7 +14250,7 @@
       <c r="N286" s="22"/>
       <c r="O286" s="22"/>
     </row>
-    <row r="287" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="287" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A287" s="22" t="s">
         <v>869</v>
       </c>
@@ -14275,7 +14279,7 @@
       <c r="N287" s="22"/>
       <c r="O287" s="22"/>
     </row>
-    <row r="288" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="288" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A288" s="22" t="s">
         <v>871</v>
       </c>
@@ -14306,7 +14310,7 @@
       <c r="N288" s="22"/>
       <c r="O288" s="22"/>
     </row>
-    <row r="289" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="289" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A289" s="22" t="s">
         <v>874</v>
       </c>
@@ -14339,7 +14343,7 @@
       <c r="N289" s="22"/>
       <c r="O289" s="22"/>
     </row>
-    <row r="290" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="290" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A290" s="22" t="s">
         <v>876</v>
       </c>
@@ -14372,7 +14376,7 @@
       <c r="N290" s="22"/>
       <c r="O290" s="22"/>
     </row>
-    <row r="291" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="291" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A291" s="22" t="s">
         <v>879</v>
       </c>
@@ -14403,7 +14407,7 @@
       <c r="N291" s="22"/>
       <c r="O291" s="22"/>
     </row>
-    <row r="292" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="292" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A292" s="22" t="s">
         <v>881</v>
       </c>
@@ -14436,7 +14440,7 @@
       <c r="N292" s="22"/>
       <c r="O292" s="22"/>
     </row>
-    <row r="293" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="293" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A293" s="22" t="s">
         <v>883</v>
       </c>
@@ -14467,7 +14471,7 @@
       <c r="N293" s="22"/>
       <c r="O293" s="22"/>
     </row>
-    <row r="294" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="294" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A294" s="22" t="s">
         <v>885</v>
       </c>
@@ -14496,7 +14500,7 @@
       <c r="N294" s="22"/>
       <c r="O294" s="22"/>
     </row>
-    <row r="295" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="295" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A295" s="22" t="s">
         <v>888</v>
       </c>
@@ -14527,7 +14531,7 @@
       <c r="N295" s="22"/>
       <c r="O295" s="22"/>
     </row>
-    <row r="296" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="296" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A296" s="22" t="s">
         <v>891</v>
       </c>
@@ -14558,7 +14562,7 @@
       <c r="N296" s="22"/>
       <c r="O296" s="22"/>
     </row>
-    <row r="297" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="297" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A297" s="22"/>
       <c r="B297" s="22"/>
       <c r="C297" s="22"/>
@@ -14575,7 +14579,7 @@
       <c r="N297" s="22"/>
       <c r="O297" s="22"/>
     </row>
-    <row r="298" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="298" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A298" s="22"/>
       <c r="B298" s="22"/>
       <c r="C298" s="22"/>
@@ -14592,7 +14596,7 @@
       <c r="N298" s="22"/>
       <c r="O298" s="22"/>
     </row>
-    <row r="299" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="299" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A299" s="22"/>
       <c r="B299" s="22"/>
       <c r="C299" s="22"/>
@@ -14609,7 +14613,7 @@
       <c r="N299" s="22"/>
       <c r="O299" s="22"/>
     </row>
-    <row r="300" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="300" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A300" s="22"/>
       <c r="B300" s="22"/>
       <c r="C300" s="22"/>
@@ -14626,7 +14630,7 @@
       <c r="N300" s="22"/>
       <c r="O300" s="22"/>
     </row>
-    <row r="301" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="301" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A301" s="22"/>
       <c r="B301" s="22"/>
       <c r="C301" s="22"/>
@@ -14651,19 +14655,19 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E8EAB12-F5F9-41AB-9BD4-DE62DD666612}">
-  <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="43.41796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.26171875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.41796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="43" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -14683,7 +14687,7 @@
         <v>1498</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>570</v>
       </c>
@@ -14694,7 +14698,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C3" t="s">
         <v>177</v>
       </c>
@@ -14705,7 +14709,7 @@
         <v>1501</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>171</v>
       </c>
@@ -14716,7 +14720,7 @@
         <v>1501</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B5" s="5" t="s">
         <v>95</v>
       </c>
@@ -14731,7 +14735,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B6" s="7" t="s">
         <v>600</v>
       </c>
@@ -14745,7 +14749,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C7" t="s">
         <v>265</v>
       </c>
@@ -14759,7 +14763,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C8" t="s">
         <v>154</v>
       </c>
@@ -14773,7 +14777,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B9" s="7" t="s">
         <v>631</v>
       </c>
@@ -14788,7 +14792,10 @@
         <v>1501</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C10" t="s">
+        <v>75</v>
+      </c>
       <c r="D10" t="s">
         <v>1502</v>
       </c>
@@ -14799,22 +14806,18 @@
         <v>1501</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" t="s">
-        <v>75</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AC19BE2-DBC7-4954-93EF-DBA4AAEF9781}">
   <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1503</v>
       </c>
@@ -14822,7 +14825,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>4001</v>
       </c>
@@ -14830,7 +14833,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>4002</v>
       </c>
@@ -14838,7 +14841,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>4003</v>
       </c>
@@ -14846,7 +14849,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4004</v>
       </c>
@@ -14854,7 +14857,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>4005</v>
       </c>
@@ -14862,7 +14865,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>4006</v>
       </c>
@@ -14870,7 +14873,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>4007</v>
       </c>
@@ -14878,7 +14881,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>4008</v>
       </c>
@@ -14886,7 +14889,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>4009</v>
       </c>
@@ -14894,7 +14897,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>4010</v>
       </c>
@@ -14902,7 +14905,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>4011</v>
       </c>
@@ -14910,7 +14913,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>4012</v>
       </c>
@@ -14918,7 +14921,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>4013</v>
       </c>
@@ -14926,7 +14929,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>4014</v>
       </c>
@@ -14934,7 +14937,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>4015</v>
       </c>
@@ -14942,7 +14945,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>4016</v>
       </c>
@@ -14958,14 +14961,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F09C4878-4F09-4069-B809-852DC4C099A1}">
   <dimension ref="A1:BK115"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="58.578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="46" width="12.41796875" customWidth="1"/>
-    <col min="47" max="47" width="19.83984375" customWidth="1"/>
+    <col min="2" max="2" width="58.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="46" width="12.5" customWidth="1"/>
+    <col min="47" max="47" width="19.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>893</v>
       </c>
@@ -15156,7 +15159,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="2" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A2" s="15">
         <v>2001</v>
       </c>
@@ -15239,7 +15242,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="3" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A3" s="15">
         <v>2002</v>
       </c>
@@ -15318,7 +15321,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="4" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A4" s="15">
         <v>2003</v>
       </c>
@@ -15395,7 +15398,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="5" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A5" s="15">
         <v>2004</v>
       </c>
@@ -15476,7 +15479,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="6" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A6" s="15">
         <v>2005</v>
       </c>
@@ -15559,7 +15562,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="7" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A7" s="15">
         <v>2006</v>
       </c>
@@ -15640,7 +15643,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="8" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A8" s="15">
         <v>2007</v>
       </c>
@@ -15721,7 +15724,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="9" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A9" s="15">
         <v>2008</v>
       </c>
@@ -15798,7 +15801,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="10" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A10" s="15">
         <v>2009</v>
       </c>
@@ -15875,7 +15878,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="11" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A11" s="15">
         <v>2010</v>
       </c>
@@ -15956,7 +15959,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="12" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A12" s="15">
         <v>2011</v>
       </c>
@@ -16035,7 +16038,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="13" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A13" s="15">
         <v>2012</v>
       </c>
@@ -16114,7 +16117,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="14" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A14" s="15">
         <v>2013</v>
       </c>
@@ -16199,7 +16202,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="15" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A15" s="15">
         <v>2014</v>
       </c>
@@ -16280,7 +16283,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="16" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A16" s="15">
         <v>2015</v>
       </c>
@@ -16363,7 +16366,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="17" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A17" s="15">
         <v>2016</v>
       </c>
@@ -16444,7 +16447,7 @@
         <v>966</v>
       </c>
     </row>
-    <row r="18" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A18" s="15">
         <v>2017</v>
       </c>
@@ -16521,7 +16524,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="19" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A19" s="15">
         <v>2018</v>
       </c>
@@ -16602,7 +16605,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="20" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A20" s="15">
         <v>2019</v>
       </c>
@@ -16685,7 +16688,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="21" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A21" s="15">
         <v>2020</v>
       </c>
@@ -16762,7 +16765,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="22" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A22" s="15">
         <v>2021</v>
       </c>
@@ -16841,7 +16844,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="23" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A23" s="15">
         <v>2022</v>
       </c>
@@ -16922,7 +16925,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="24" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A24" s="15">
         <v>2023</v>
       </c>
@@ -17003,7 +17006,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="25" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A25" s="15">
         <v>2024</v>
       </c>
@@ -17080,7 +17083,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="26" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A26" s="15">
         <v>2025</v>
       </c>
@@ -17159,7 +17162,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="27" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A27" s="15">
         <v>2026</v>
       </c>
@@ -17240,7 +17243,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="28" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A28" s="15">
         <v>2027</v>
       </c>
@@ -17319,7 +17322,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="29" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A29" s="15">
         <v>2028</v>
       </c>
@@ -17396,7 +17399,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="30" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A30" s="15">
         <v>2029</v>
       </c>
@@ -17475,7 +17478,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="31" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A31" s="15">
         <v>2030</v>
       </c>
@@ -17552,7 +17555,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="32" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A32" s="15">
         <v>2031</v>
       </c>
@@ -17645,7 +17648,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="33" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A33" s="15">
         <v>2032</v>
       </c>
@@ -17726,7 +17729,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="34" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A34" s="15">
         <v>2033</v>
       </c>
@@ -17821,7 +17824,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="35" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A35" s="15">
         <v>2034</v>
       </c>
@@ -17900,7 +17903,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="36" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A36" s="15">
         <v>2035</v>
       </c>
@@ -17979,7 +17982,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="37" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A37" s="15">
         <v>2036</v>
       </c>
@@ -18060,7 +18063,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="38" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A38" s="15">
         <v>2037</v>
       </c>
@@ -18139,7 +18142,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="39" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A39" s="15">
         <v>2038</v>
       </c>
@@ -18222,7 +18225,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="40" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A40" s="15">
         <v>2039</v>
       </c>
@@ -18307,7 +18310,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="41" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A41" s="15">
         <v>2040</v>
       </c>
@@ -18384,7 +18387,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="42" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A42" s="15">
         <v>2041</v>
       </c>
@@ -18465,7 +18468,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="43" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A43" s="15">
         <v>2042</v>
       </c>
@@ -18544,7 +18547,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="44" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A44" s="15">
         <v>2043</v>
       </c>
@@ -18625,7 +18628,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="45" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A45" s="15">
         <v>2044</v>
       </c>
@@ -18704,7 +18707,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="46" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A46" s="15">
         <v>2045</v>
       </c>
@@ -18783,7 +18786,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="47" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A47" s="15">
         <v>2046</v>
       </c>
@@ -18862,7 +18865,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="48" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A48" s="15">
         <v>2047</v>
       </c>
@@ -18943,7 +18946,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="49" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A49" s="15">
         <v>2048</v>
       </c>
@@ -19022,7 +19025,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="50" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A50" s="15">
         <v>2049</v>
       </c>
@@ -19103,7 +19106,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="51" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A51" s="15">
         <v>2050</v>
       </c>
@@ -19180,7 +19183,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="52" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A52" s="15">
         <v>2051</v>
       </c>
@@ -19257,7 +19260,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="53" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A53" s="15">
         <v>2052</v>
       </c>
@@ -19340,7 +19343,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="54" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A54" s="15">
         <v>2053</v>
       </c>
@@ -19417,7 +19420,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="55" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A55" s="15">
         <v>2054</v>
       </c>
@@ -19494,7 +19497,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="56" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A56" s="15">
         <v>2055</v>
       </c>
@@ -19575,7 +19578,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="57" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A57" s="15">
         <v>2056</v>
       </c>
@@ -19654,7 +19657,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="58" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A58" s="15">
         <v>2057</v>
       </c>
@@ -19735,7 +19738,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="59" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A59" s="15">
         <v>2058</v>
       </c>
@@ -19816,7 +19819,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="60" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A60" s="15">
         <v>2059</v>
       </c>
@@ -19893,7 +19896,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="61" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A61" s="15">
         <v>2060</v>
       </c>
@@ -19978,7 +19981,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="62" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A62" s="15">
         <v>2061</v>
       </c>
@@ -20055,7 +20058,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="63" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A63" s="15">
         <v>2062</v>
       </c>
@@ -20134,7 +20137,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="64" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A64" s="15">
         <v>2063</v>
       </c>
@@ -20215,7 +20218,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="65" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A65" s="15">
         <v>2064</v>
       </c>
@@ -20292,7 +20295,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="66" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A66" s="15">
         <v>2065</v>
       </c>
@@ -20379,7 +20382,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="67" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A67" s="15">
         <v>2066</v>
       </c>
@@ -20464,7 +20467,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="68" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A68" s="15">
         <v>2067</v>
       </c>
@@ -20541,7 +20544,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="69" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A69" s="15">
         <v>2068</v>
       </c>
@@ -20628,7 +20631,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="70" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A70" s="15">
         <v>2069</v>
       </c>
@@ -20707,7 +20710,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="71" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A71" s="15">
         <v>2070</v>
       </c>
@@ -20784,7 +20787,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="72" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A72" s="15">
         <v>2071</v>
       </c>
@@ -20863,7 +20866,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="73" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A73" s="15">
         <v>2072</v>
       </c>
@@ -20940,7 +20943,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="74" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A74" s="15">
         <v>2073</v>
       </c>
@@ -21017,7 +21020,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="75" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A75" s="15">
         <v>2074</v>
       </c>
@@ -21098,7 +21101,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="76" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A76" s="15">
         <v>2075</v>
       </c>
@@ -21179,7 +21182,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="77" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A77" s="15">
         <v>2076</v>
       </c>
@@ -21260,7 +21263,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="78" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A78" s="15">
         <v>2077</v>
       </c>
@@ -21337,7 +21340,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="79" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A79" s="15">
         <v>2078</v>
       </c>
@@ -21418,7 +21421,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="80" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A80" s="15">
         <v>2079</v>
       </c>
@@ -21499,7 +21502,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="81" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A81" s="15">
         <v>2080</v>
       </c>
@@ -21582,7 +21585,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="82" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A82" s="15">
         <v>2081</v>
       </c>
@@ -21669,7 +21672,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="83" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A83" s="15">
         <v>2082</v>
       </c>
@@ -21750,7 +21753,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="84" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A84" s="15">
         <v>2083</v>
       </c>
@@ -21829,7 +21832,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="85" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A85" s="15">
         <v>2084</v>
       </c>
@@ -21914,7 +21917,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="86" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A86" s="15">
         <v>2085</v>
       </c>
@@ -21993,7 +21996,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="87" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A87" s="15">
         <v>2086</v>
       </c>
@@ -22072,7 +22075,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="88" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A88" s="15">
         <v>2087</v>
       </c>
@@ -22151,7 +22154,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="89" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A89" s="15">
         <v>2088</v>
       </c>
@@ -22232,7 +22235,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="90" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A90" s="15">
         <v>2089</v>
       </c>
@@ -22309,7 +22312,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="91" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A91" s="15">
         <v>2090</v>
       </c>
@@ -22388,7 +22391,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="92" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A92" s="15">
         <v>2091</v>
       </c>
@@ -22465,7 +22468,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="93" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A93" s="15">
         <v>2092</v>
       </c>
@@ -22542,7 +22545,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="94" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A94" s="15">
         <v>2093</v>
       </c>
@@ -22621,7 +22624,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="95" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A95" s="15">
         <v>2094</v>
       </c>
@@ -22698,7 +22701,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="96" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A96" s="15">
         <v>2095</v>
       </c>
@@ -22785,7 +22788,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="97" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A97" s="15">
         <v>2096</v>
       </c>
@@ -22864,7 +22867,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="98" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A98" s="15">
         <v>2097</v>
       </c>
@@ -22941,7 +22944,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="99" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A99" s="15">
         <v>2098</v>
       </c>
@@ -23022,7 +23025,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="100" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A100" s="15">
         <v>2099</v>
       </c>
@@ -23099,7 +23102,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="101" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A101" s="15">
         <v>2100</v>
       </c>
@@ -23178,7 +23181,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="102" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A102" s="15">
         <v>2101</v>
       </c>
@@ -23257,7 +23260,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="103" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A103" s="15">
         <v>2102</v>
       </c>
@@ -23334,7 +23337,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="104" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A104" s="15">
         <v>2103</v>
       </c>
@@ -23413,7 +23416,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="105" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A105" s="15">
         <v>2104</v>
       </c>
@@ -23590,7 +23593,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="106" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A106" s="15">
         <v>2105</v>
       </c>
@@ -23769,7 +23772,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="107" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A107" s="15">
         <v>2106</v>
       </c>
@@ -23958,7 +23961,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="108" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A108" s="15">
         <v>2107</v>
       </c>
@@ -24121,7 +24124,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="109" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A109" s="15">
         <v>2108</v>
       </c>
@@ -24302,7 +24305,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="110" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A110" s="15">
         <v>2109</v>
       </c>
@@ -24461,7 +24464,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="111" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A111" s="15">
         <v>2110</v>
       </c>
@@ -24634,7 +24637,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="112" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A112" s="15">
         <v>2111</v>
       </c>
@@ -24793,7 +24796,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="113" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="113" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A113" s="15">
         <v>2112</v>
       </c>
@@ -24932,7 +24935,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="114" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A114" s="15">
         <v>2113</v>
       </c>
@@ -25097,7 +25100,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="115" spans="1:63" x14ac:dyDescent="0.55000000000000004">
+    <row r="115" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A115" s="15">
         <v>2114</v>
       </c>
@@ -25282,12 +25285,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B2F8A48-D5B8-4D6F-A7AE-1C5019048303}">
   <dimension ref="A1:J212"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>1059</v>
       </c>
@@ -25319,7 +25322,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="15">
         <v>3001</v>
       </c>
@@ -25339,7 +25342,7 @@
       <c r="I2" s="15"/>
       <c r="J2" s="15"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="15">
         <v>3002</v>
       </c>
@@ -25359,7 +25362,7 @@
       <c r="I3" s="15"/>
       <c r="J3" s="15"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="15">
         <v>3003</v>
       </c>
@@ -25377,7 +25380,7 @@
       <c r="I4" s="15"/>
       <c r="J4" s="15"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="15">
         <v>3004</v>
       </c>
@@ -25399,7 +25402,7 @@
       <c r="I5" s="15"/>
       <c r="J5" s="15"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="15">
         <v>3005</v>
       </c>
@@ -25419,7 +25422,7 @@
       <c r="I6" s="15"/>
       <c r="J6" s="15"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="15">
         <v>3006</v>
       </c>
@@ -25447,7 +25450,7 @@
       <c r="I7" s="15"/>
       <c r="J7" s="15"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="15">
         <v>3007</v>
       </c>
@@ -25467,7 +25470,7 @@
       <c r="I8" s="15"/>
       <c r="J8" s="15"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="15">
         <v>3008</v>
       </c>
@@ -25485,7 +25488,7 @@
       <c r="I9" s="15"/>
       <c r="J9" s="15"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="15">
         <v>3009</v>
       </c>
@@ -25507,7 +25510,7 @@
       <c r="I10" s="15"/>
       <c r="J10" s="15"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="15">
         <v>3010</v>
       </c>
@@ -25527,7 +25530,7 @@
       <c r="I11" s="15"/>
       <c r="J11" s="15"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="15">
         <v>3011</v>
       </c>
@@ -25547,7 +25550,7 @@
       <c r="I12" s="15"/>
       <c r="J12" s="15"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="15">
         <v>3012</v>
       </c>
@@ -25567,7 +25570,7 @@
       <c r="I13" s="15"/>
       <c r="J13" s="15"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="15">
         <v>3013</v>
       </c>
@@ -25585,7 +25588,7 @@
       <c r="I14" s="15"/>
       <c r="J14" s="15"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="15">
         <v>3014</v>
       </c>
@@ -25603,7 +25606,7 @@
       <c r="I15" s="15"/>
       <c r="J15" s="15"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="15">
         <v>3015</v>
       </c>
@@ -25629,7 +25632,7 @@
       <c r="I16" s="15"/>
       <c r="J16" s="15"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="15">
         <v>3016</v>
       </c>
@@ -25647,7 +25650,7 @@
       <c r="I17" s="15"/>
       <c r="J17" s="15"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="15">
         <v>3017</v>
       </c>
@@ -25669,7 +25672,7 @@
       <c r="I18" s="15"/>
       <c r="J18" s="15"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="15">
         <v>3018</v>
       </c>
@@ -25691,7 +25694,7 @@
       <c r="I19" s="15"/>
       <c r="J19" s="15"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="15">
         <v>3019</v>
       </c>
@@ -25709,7 +25712,7 @@
       <c r="I20" s="15"/>
       <c r="J20" s="15"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="15">
         <v>3020</v>
       </c>
@@ -25729,7 +25732,7 @@
       <c r="I21" s="15"/>
       <c r="J21" s="15"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="15">
         <v>3021</v>
       </c>
@@ -25751,7 +25754,7 @@
       <c r="I22" s="15"/>
       <c r="J22" s="15"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="15">
         <v>3022</v>
       </c>
@@ -25773,7 +25776,7 @@
       <c r="I23" s="15"/>
       <c r="J23" s="15"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="15">
         <v>3023</v>
       </c>
@@ -25791,7 +25794,7 @@
       <c r="I24" s="15"/>
       <c r="J24" s="15"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="15">
         <v>3024</v>
       </c>
@@ -25811,7 +25814,7 @@
       <c r="I25" s="15"/>
       <c r="J25" s="15"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="15">
         <v>3025</v>
       </c>
@@ -25833,7 +25836,7 @@
       <c r="I26" s="15"/>
       <c r="J26" s="15"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="15">
         <v>3026</v>
       </c>
@@ -25853,7 +25856,7 @@
       <c r="I27" s="15"/>
       <c r="J27" s="15"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="15">
         <v>3027</v>
       </c>
@@ -25871,7 +25874,7 @@
       <c r="I28" s="15"/>
       <c r="J28" s="15"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="15">
         <v>3028</v>
       </c>
@@ -25891,7 +25894,7 @@
       <c r="I29" s="15"/>
       <c r="J29" s="15"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="15">
         <v>3029</v>
       </c>
@@ -25917,7 +25920,7 @@
       <c r="I30" s="15"/>
       <c r="J30" s="15"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="15">
         <v>3030</v>
       </c>
@@ -25937,7 +25940,7 @@
       <c r="I31" s="15"/>
       <c r="J31" s="15"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="15">
         <v>3031</v>
       </c>
@@ -25957,7 +25960,7 @@
       <c r="I32" s="15"/>
       <c r="J32" s="15"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" s="15">
         <v>3032</v>
       </c>
@@ -25977,7 +25980,7 @@
       <c r="I33" s="15"/>
       <c r="J33" s="15"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="15">
         <v>3033</v>
       </c>
@@ -25997,7 +26000,7 @@
       <c r="I34" s="15"/>
       <c r="J34" s="15"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" s="15">
         <v>3034</v>
       </c>
@@ -26017,7 +26020,7 @@
       <c r="I35" s="15"/>
       <c r="J35" s="15"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" s="15">
         <v>3035</v>
       </c>
@@ -26035,7 +26038,7 @@
       <c r="I36" s="15"/>
       <c r="J36" s="15"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="15">
         <v>3036</v>
       </c>
@@ -26057,7 +26060,7 @@
       <c r="I37" s="15"/>
       <c r="J37" s="15"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" s="15">
         <v>3037</v>
       </c>
@@ -26077,7 +26080,7 @@
       <c r="I38" s="15"/>
       <c r="J38" s="15"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" s="15">
         <v>3038</v>
       </c>
@@ -26099,7 +26102,7 @@
       <c r="I39" s="15"/>
       <c r="J39" s="15"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" s="15">
         <v>3039</v>
       </c>
@@ -26119,7 +26122,7 @@
       <c r="I40" s="15"/>
       <c r="J40" s="15"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" s="15">
         <v>3040</v>
       </c>
@@ -26139,7 +26142,7 @@
       <c r="I41" s="15"/>
       <c r="J41" s="15"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" s="15">
         <v>3041</v>
       </c>
@@ -26159,7 +26162,7 @@
       <c r="I42" s="15"/>
       <c r="J42" s="15"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" s="15">
         <v>3042</v>
       </c>
@@ -26179,7 +26182,7 @@
       <c r="I43" s="15"/>
       <c r="J43" s="15"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" s="15">
         <v>3043</v>
       </c>
@@ -26197,7 +26200,7 @@
       <c r="I44" s="15"/>
       <c r="J44" s="15"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" s="15">
         <v>3044</v>
       </c>
@@ -26215,7 +26218,7 @@
       <c r="I45" s="15"/>
       <c r="J45" s="15"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" s="15">
         <v>3045</v>
       </c>
@@ -26233,7 +26236,7 @@
       <c r="I46" s="15"/>
       <c r="J46" s="15"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" s="15">
         <v>3046</v>
       </c>
@@ -26251,7 +26254,7 @@
       <c r="I47" s="15"/>
       <c r="J47" s="15"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" s="15">
         <v>3047</v>
       </c>
@@ -26269,7 +26272,7 @@
       <c r="I48" s="15"/>
       <c r="J48" s="15"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" s="15">
         <v>3048</v>
       </c>
@@ -26287,7 +26290,7 @@
       <c r="I49" s="15"/>
       <c r="J49" s="15"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" s="15">
         <v>3049</v>
       </c>
@@ -26307,7 +26310,7 @@
       <c r="I50" s="15"/>
       <c r="J50" s="15"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" s="15">
         <v>3050</v>
       </c>
@@ -26329,7 +26332,7 @@
       <c r="I51" s="15"/>
       <c r="J51" s="15"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" s="15">
         <v>3051</v>
       </c>
@@ -26351,7 +26354,7 @@
       <c r="I52" s="15"/>
       <c r="J52" s="15"/>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53" s="15">
         <v>3052</v>
       </c>
@@ -26369,7 +26372,7 @@
       <c r="I53" s="15"/>
       <c r="J53" s="15"/>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54" s="15">
         <v>3053</v>
       </c>
@@ -26393,7 +26396,7 @@
       <c r="I54" s="15"/>
       <c r="J54" s="15"/>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" s="15">
         <v>3054</v>
       </c>
@@ -26411,7 +26414,7 @@
       <c r="I55" s="15"/>
       <c r="J55" s="15"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A56" s="15">
         <v>3055</v>
       </c>
@@ -26431,7 +26434,7 @@
       <c r="I56" s="15"/>
       <c r="J56" s="15"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57" s="15">
         <v>3056</v>
       </c>
@@ -26449,7 +26452,7 @@
       <c r="I57" s="15"/>
       <c r="J57" s="15"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A58" s="15">
         <v>3057</v>
       </c>
@@ -26467,7 +26470,7 @@
       <c r="I58" s="15"/>
       <c r="J58" s="15"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A59" s="15">
         <v>3058</v>
       </c>
@@ -26489,7 +26492,7 @@
       <c r="I59" s="15"/>
       <c r="J59" s="15"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A60" s="15">
         <v>3059</v>
       </c>
@@ -26509,7 +26512,7 @@
       <c r="I60" s="15"/>
       <c r="J60" s="15"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" s="15">
         <v>3060</v>
       </c>
@@ -26527,7 +26530,7 @@
       <c r="I61" s="15"/>
       <c r="J61" s="15"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A62" s="15">
         <v>3061</v>
       </c>
@@ -26551,7 +26554,7 @@
       <c r="I62" s="15"/>
       <c r="J62" s="15"/>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" s="15">
         <v>3062</v>
       </c>
@@ -26571,7 +26574,7 @@
       <c r="I63" s="15"/>
       <c r="J63" s="15"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A64" s="15">
         <v>3063</v>
       </c>
@@ -26589,7 +26592,7 @@
       <c r="I64" s="15"/>
       <c r="J64" s="15"/>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A65" s="15">
         <v>3064</v>
       </c>
@@ -26609,7 +26612,7 @@
       <c r="I65" s="15"/>
       <c r="J65" s="15"/>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A66" s="15">
         <v>3065</v>
       </c>
@@ -26627,7 +26630,7 @@
       <c r="I66" s="15"/>
       <c r="J66" s="15"/>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A67" s="15">
         <v>3066</v>
       </c>
@@ -26649,7 +26652,7 @@
       <c r="I67" s="15"/>
       <c r="J67" s="15"/>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A68" s="15">
         <v>3067</v>
       </c>
@@ -26671,7 +26674,7 @@
       <c r="I68" s="15"/>
       <c r="J68" s="15"/>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A69" s="15">
         <v>3068</v>
       </c>
@@ -26689,7 +26692,7 @@
       <c r="I69" s="15"/>
       <c r="J69" s="15"/>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A70" s="15">
         <v>3069</v>
       </c>
@@ -26711,7 +26714,7 @@
       <c r="I70" s="15"/>
       <c r="J70" s="15"/>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A71" s="15">
         <v>3070</v>
       </c>
@@ -26733,7 +26736,7 @@
       <c r="I71" s="15"/>
       <c r="J71" s="15"/>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A72" s="15">
         <v>3071</v>
       </c>
@@ -26751,7 +26754,7 @@
       <c r="I72" s="15"/>
       <c r="J72" s="15"/>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A73" s="15">
         <v>3072</v>
       </c>
@@ -26771,7 +26774,7 @@
       <c r="I73" s="15"/>
       <c r="J73" s="15"/>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A74" s="15">
         <v>3073</v>
       </c>
@@ -26793,7 +26796,7 @@
       <c r="I74" s="15"/>
       <c r="J74" s="15"/>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A75" s="15">
         <v>3074</v>
       </c>
@@ -26813,7 +26816,7 @@
       <c r="I75" s="15"/>
       <c r="J75" s="15"/>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A76" s="15">
         <v>3075</v>
       </c>
@@ -26833,7 +26836,7 @@
       <c r="I76" s="15"/>
       <c r="J76" s="15"/>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A77" s="15">
         <v>3076</v>
       </c>
@@ -26853,7 +26856,7 @@
       <c r="I77" s="15"/>
       <c r="J77" s="15"/>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A78" s="15">
         <v>3077</v>
       </c>
@@ -26873,7 +26876,7 @@
       <c r="I78" s="15"/>
       <c r="J78" s="15"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A79" s="15">
         <v>3078</v>
       </c>
@@ -26895,7 +26898,7 @@
       <c r="I79" s="15"/>
       <c r="J79" s="15"/>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A80" s="15">
         <v>3079</v>
       </c>
@@ -26913,7 +26916,7 @@
       <c r="I80" s="15"/>
       <c r="J80" s="15"/>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A81" s="15">
         <v>3080</v>
       </c>
@@ -26933,7 +26936,7 @@
       <c r="I81" s="15"/>
       <c r="J81" s="15"/>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A82" s="15">
         <v>3081</v>
       </c>
@@ -26951,7 +26954,7 @@
       <c r="I82" s="15"/>
       <c r="J82" s="15"/>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A83" s="15">
         <v>3082</v>
       </c>
@@ -26969,7 +26972,7 @@
       <c r="I83" s="15"/>
       <c r="J83" s="15"/>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A84" s="15">
         <v>3083</v>
       </c>
@@ -26989,7 +26992,7 @@
       <c r="I84" s="15"/>
       <c r="J84" s="15"/>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A85" s="15">
         <v>3084</v>
       </c>
@@ -27007,7 +27010,7 @@
       <c r="I85" s="15"/>
       <c r="J85" s="15"/>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A86" s="15">
         <v>3085</v>
       </c>
@@ -27027,7 +27030,7 @@
       <c r="I86" s="15"/>
       <c r="J86" s="15"/>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A87" s="15">
         <v>3086</v>
       </c>
@@ -27047,7 +27050,7 @@
       <c r="I87" s="15"/>
       <c r="J87" s="15"/>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A88" s="15">
         <v>3087</v>
       </c>
@@ -27065,7 +27068,7 @@
       <c r="I88" s="15"/>
       <c r="J88" s="15"/>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A89" s="15">
         <v>3088</v>
       </c>
@@ -27083,7 +27086,7 @@
       <c r="I89" s="15"/>
       <c r="J89" s="15"/>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A90" s="15">
         <v>3089</v>
       </c>
@@ -27101,7 +27104,7 @@
       <c r="I90" s="15"/>
       <c r="J90" s="15"/>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A91" s="15">
         <v>3090</v>
       </c>
@@ -27121,7 +27124,7 @@
       <c r="I91" s="15"/>
       <c r="J91" s="15"/>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A92" s="15">
         <v>3091</v>
       </c>
@@ -27139,7 +27142,7 @@
       <c r="I92" s="15"/>
       <c r="J92" s="15"/>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A93" s="15">
         <v>3092</v>
       </c>
@@ -27159,7 +27162,7 @@
       <c r="I93" s="15"/>
       <c r="J93" s="15"/>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A94" s="15">
         <v>3093</v>
       </c>
@@ -27177,7 +27180,7 @@
       <c r="I94" s="15"/>
       <c r="J94" s="15"/>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A95" s="15">
         <v>3094</v>
       </c>
@@ -27203,7 +27206,7 @@
       <c r="I95" s="15"/>
       <c r="J95" s="15"/>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A96" s="15">
         <v>3095</v>
       </c>
@@ -27223,7 +27226,7 @@
       <c r="I96" s="15"/>
       <c r="J96" s="15"/>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A97" s="15">
         <v>3096</v>
       </c>
@@ -27243,7 +27246,7 @@
       <c r="I97" s="15"/>
       <c r="J97" s="15"/>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A98" s="15">
         <v>3097</v>
       </c>
@@ -27269,7 +27272,7 @@
       <c r="I98" s="15"/>
       <c r="J98" s="15"/>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A99" s="15">
         <v>3098</v>
       </c>
@@ -27291,7 +27294,7 @@
       <c r="I99" s="15"/>
       <c r="J99" s="15"/>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A100" s="15">
         <v>3099</v>
       </c>
@@ -27313,7 +27316,7 @@
       <c r="I100" s="15"/>
       <c r="J100" s="15"/>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A101" s="15">
         <v>3100</v>
       </c>
@@ -27339,7 +27342,7 @@
       <c r="I101" s="15"/>
       <c r="J101" s="15"/>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A102" s="15">
         <v>3101</v>
       </c>
@@ -27361,7 +27364,7 @@
       <c r="I102" s="15"/>
       <c r="J102" s="15"/>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A103" s="15">
         <v>3102</v>
       </c>
@@ -27387,7 +27390,7 @@
       <c r="I103" s="15"/>
       <c r="J103" s="15"/>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A104" s="15">
         <v>3103</v>
       </c>
@@ -27413,7 +27416,7 @@
       <c r="I104" s="15"/>
       <c r="J104" s="15"/>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A105" s="15">
         <v>3104</v>
       </c>
@@ -27435,7 +27438,7 @@
       <c r="I105" s="15"/>
       <c r="J105" s="15"/>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A106" s="15">
         <v>3105</v>
       </c>
@@ -27459,7 +27462,7 @@
       <c r="I106" s="15"/>
       <c r="J106" s="15"/>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A107" s="15">
         <v>3106</v>
       </c>
@@ -27477,7 +27480,7 @@
       <c r="I107" s="15"/>
       <c r="J107" s="15"/>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A108" s="15">
         <v>3107</v>
       </c>
@@ -27505,7 +27508,7 @@
       <c r="I108" s="15"/>
       <c r="J108" s="15"/>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A109" s="15">
         <v>3108</v>
       </c>
@@ -27531,7 +27534,7 @@
       <c r="I109" s="15"/>
       <c r="J109" s="15"/>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A110" s="15">
         <v>3109</v>
       </c>
@@ -27551,7 +27554,7 @@
       <c r="I110" s="15"/>
       <c r="J110" s="15"/>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A111" s="15">
         <v>3110</v>
       </c>
@@ -27575,7 +27578,7 @@
       <c r="I111" s="15"/>
       <c r="J111" s="15"/>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A112" s="15">
         <v>3111</v>
       </c>
@@ -27595,7 +27598,7 @@
       <c r="I112" s="15"/>
       <c r="J112" s="15"/>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A113" s="15">
         <v>3112</v>
       </c>
@@ -27615,7 +27618,7 @@
       <c r="I113" s="15"/>
       <c r="J113" s="15"/>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A114" s="15">
         <v>3113</v>
       </c>
@@ -27635,7 +27638,7 @@
       <c r="I114" s="15"/>
       <c r="J114" s="15"/>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A115" s="15">
         <v>3114</v>
       </c>
@@ -27653,7 +27656,7 @@
       <c r="I115" s="15"/>
       <c r="J115" s="15"/>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A116" s="15">
         <v>3115</v>
       </c>
@@ -27683,7 +27686,7 @@
       </c>
       <c r="J116" s="15"/>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A117" s="15">
         <v>3116</v>
       </c>
@@ -27707,7 +27710,7 @@
       <c r="I117" s="15"/>
       <c r="J117" s="15"/>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A118" s="15">
         <v>3117</v>
       </c>
@@ -27733,7 +27736,7 @@
       <c r="I118" s="15"/>
       <c r="J118" s="15"/>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A119" s="15">
         <v>3118</v>
       </c>
@@ -27751,7 +27754,7 @@
       <c r="I119" s="15"/>
       <c r="J119" s="15"/>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A120" s="15">
         <v>3119</v>
       </c>
@@ -27775,7 +27778,7 @@
       <c r="I120" s="15"/>
       <c r="J120" s="15"/>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A121" s="15">
         <v>3120</v>
       </c>
@@ -27803,7 +27806,7 @@
       <c r="I121" s="15"/>
       <c r="J121" s="15"/>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A122" s="15">
         <v>3121</v>
       </c>
@@ -27821,7 +27824,7 @@
       <c r="I122" s="15"/>
       <c r="J122" s="15"/>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A123" s="15">
         <v>3122</v>
       </c>
@@ -27845,7 +27848,7 @@
       <c r="I123" s="15"/>
       <c r="J123" s="15"/>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A124" s="15">
         <v>3123</v>
       </c>
@@ -27869,7 +27872,7 @@
       <c r="I124" s="15"/>
       <c r="J124" s="15"/>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A125" s="15">
         <v>3124</v>
       </c>
@@ -27891,7 +27894,7 @@
       <c r="I125" s="15"/>
       <c r="J125" s="15"/>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A126" s="15">
         <v>3125</v>
       </c>
@@ -27917,7 +27920,7 @@
       <c r="I126" s="15"/>
       <c r="J126" s="15"/>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A127" s="15">
         <v>3126</v>
       </c>
@@ -27939,7 +27942,7 @@
       <c r="I127" s="15"/>
       <c r="J127" s="15"/>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A128" s="15">
         <v>3127</v>
       </c>
@@ -27957,7 +27960,7 @@
       <c r="I128" s="15"/>
       <c r="J128" s="15"/>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A129" s="15">
         <v>3128</v>
       </c>
@@ -27975,7 +27978,7 @@
       <c r="I129" s="15"/>
       <c r="J129" s="15"/>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A130" s="15">
         <v>3129</v>
       </c>
@@ -27999,7 +28002,7 @@
       <c r="I130" s="15"/>
       <c r="J130" s="15"/>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A131" s="15">
         <v>3130</v>
       </c>
@@ -28021,7 +28024,7 @@
       <c r="I131" s="15"/>
       <c r="J131" s="15"/>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A132" s="15">
         <v>3131</v>
       </c>
@@ -28053,7 +28056,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A133" s="15">
         <v>3132</v>
       </c>
@@ -28079,7 +28082,7 @@
       <c r="I133" s="15"/>
       <c r="J133" s="15"/>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A134" s="15">
         <v>3133</v>
       </c>
@@ -28099,7 +28102,7 @@
       <c r="I134" s="15"/>
       <c r="J134" s="15"/>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A135" s="15">
         <v>3134</v>
       </c>
@@ -28121,7 +28124,7 @@
       <c r="I135" s="15"/>
       <c r="J135" s="15"/>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A136" s="15">
         <v>3135</v>
       </c>
@@ -28141,7 +28144,7 @@
       <c r="I136" s="15"/>
       <c r="J136" s="15"/>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A137" s="15">
         <v>3136</v>
       </c>
@@ -28159,7 +28162,7 @@
       <c r="I137" s="15"/>
       <c r="J137" s="15"/>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A138" s="15">
         <v>3137</v>
       </c>
@@ -28179,7 +28182,7 @@
       <c r="I138" s="15"/>
       <c r="J138" s="15"/>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A139" s="15">
         <v>3138</v>
       </c>
@@ -28199,7 +28202,7 @@
       <c r="I139" s="15"/>
       <c r="J139" s="15"/>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A140" s="15">
         <v>3139</v>
       </c>
@@ -28217,7 +28220,7 @@
       <c r="I140" s="15"/>
       <c r="J140" s="15"/>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A141" s="15">
         <v>3140</v>
       </c>
@@ -28239,7 +28242,7 @@
       <c r="I141" s="15"/>
       <c r="J141" s="15"/>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A142" s="15">
         <v>3141</v>
       </c>
@@ -28257,7 +28260,7 @@
       <c r="I142" s="15"/>
       <c r="J142" s="15"/>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A143" s="15">
         <v>3142</v>
       </c>
@@ -28279,7 +28282,7 @@
       <c r="I143" s="15"/>
       <c r="J143" s="15"/>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A144" s="15">
         <v>3143</v>
       </c>
@@ -28303,7 +28306,7 @@
       <c r="I144" s="15"/>
       <c r="J144" s="15"/>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A145" s="15">
         <v>3144</v>
       </c>
@@ -28323,7 +28326,7 @@
       <c r="I145" s="15"/>
       <c r="J145" s="15"/>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A146" s="15">
         <v>3145</v>
       </c>
@@ -28345,7 +28348,7 @@
       <c r="I146" s="15"/>
       <c r="J146" s="15"/>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A147" s="15">
         <v>3146</v>
       </c>
@@ -28369,7 +28372,7 @@
       <c r="I147" s="15"/>
       <c r="J147" s="15"/>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A148" s="15">
         <v>3147</v>
       </c>
@@ -28387,7 +28390,7 @@
       <c r="I148" s="15"/>
       <c r="J148" s="15"/>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A149" s="15">
         <v>3148</v>
       </c>
@@ -28407,7 +28410,7 @@
       <c r="I149" s="15"/>
       <c r="J149" s="15"/>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A150" s="15">
         <v>3149</v>
       </c>
@@ -28425,7 +28428,7 @@
       <c r="I150" s="15"/>
       <c r="J150" s="15"/>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A151" s="15">
         <v>3150</v>
       </c>
@@ -28443,7 +28446,7 @@
       <c r="I151" s="15"/>
       <c r="J151" s="15"/>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A152" s="15">
         <v>3151</v>
       </c>
@@ -28463,7 +28466,7 @@
       <c r="I152" s="15"/>
       <c r="J152" s="15"/>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A153" s="15">
         <v>3152</v>
       </c>
@@ -28483,7 +28486,7 @@
       <c r="I153" s="15"/>
       <c r="J153" s="15"/>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A154" s="15">
         <v>3153</v>
       </c>
@@ -28505,7 +28508,7 @@
       <c r="I154" s="15"/>
       <c r="J154" s="15"/>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A155" s="15">
         <v>3154</v>
       </c>
@@ -28525,7 +28528,7 @@
       <c r="I155" s="15"/>
       <c r="J155" s="15"/>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A156" s="15">
         <v>3155</v>
       </c>
@@ -28543,7 +28546,7 @@
       <c r="I156" s="15"/>
       <c r="J156" s="15"/>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A157" s="15">
         <v>3156</v>
       </c>
@@ -28565,7 +28568,7 @@
       <c r="I157" s="15"/>
       <c r="J157" s="15"/>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A158" s="15">
         <v>3157</v>
       </c>
@@ -28593,7 +28596,7 @@
       <c r="I158" s="15"/>
       <c r="J158" s="15"/>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A159" s="15">
         <v>3158</v>
       </c>
@@ -28617,7 +28620,7 @@
       <c r="I159" s="15"/>
       <c r="J159" s="15"/>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A160" s="15">
         <v>3159</v>
       </c>
@@ -28635,7 +28638,7 @@
       <c r="I160" s="15"/>
       <c r="J160" s="15"/>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A161" s="15">
         <v>3160</v>
       </c>
@@ -28653,7 +28656,7 @@
       <c r="I161" s="15"/>
       <c r="J161" s="15"/>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A162" s="15">
         <v>3161</v>
       </c>
@@ -28673,7 +28676,7 @@
       <c r="I162" s="15"/>
       <c r="J162" s="15"/>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A163" s="15">
         <v>3162</v>
       </c>
@@ -28691,7 +28694,7 @@
       <c r="I163" s="15"/>
       <c r="J163" s="15"/>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A164" s="15">
         <v>3163</v>
       </c>
@@ -28713,7 +28716,7 @@
       <c r="I164" s="15"/>
       <c r="J164" s="15"/>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A165" s="15">
         <v>3164</v>
       </c>
@@ -28735,7 +28738,7 @@
       <c r="I165" s="15"/>
       <c r="J165" s="15"/>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A166" s="15">
         <v>3165</v>
       </c>
@@ -28759,7 +28762,7 @@
       <c r="I166" s="15"/>
       <c r="J166" s="15"/>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A167" s="15">
         <v>3166</v>
       </c>
@@ -28779,7 +28782,7 @@
       <c r="I167" s="15"/>
       <c r="J167" s="15"/>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A168" s="15">
         <v>3167</v>
       </c>
@@ -28803,7 +28806,7 @@
       <c r="I168" s="15"/>
       <c r="J168" s="15"/>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A169" s="15">
         <v>3168</v>
       </c>
@@ -28827,7 +28830,7 @@
       <c r="I169" s="15"/>
       <c r="J169" s="15"/>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A170" s="15">
         <v>3169</v>
       </c>
@@ -28849,7 +28852,7 @@
       <c r="I170" s="15"/>
       <c r="J170" s="15"/>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A171" s="15">
         <v>3170</v>
       </c>
@@ -28871,7 +28874,7 @@
       <c r="I171" s="15"/>
       <c r="J171" s="15"/>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A172" s="15">
         <v>3171</v>
       </c>
@@ -28893,7 +28896,7 @@
       <c r="I172" s="15"/>
       <c r="J172" s="15"/>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A173" s="15">
         <v>3172</v>
       </c>
@@ -28911,7 +28914,7 @@
       <c r="I173" s="15"/>
       <c r="J173" s="15"/>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A174" s="15">
         <v>3173</v>
       </c>
@@ -28937,7 +28940,7 @@
       <c r="I174" s="15"/>
       <c r="J174" s="15"/>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A175" s="15">
         <v>3174</v>
       </c>
@@ -28955,7 +28958,7 @@
       <c r="I175" s="15"/>
       <c r="J175" s="15"/>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A176" s="15">
         <v>3175</v>
       </c>
@@ -28979,7 +28982,7 @@
       <c r="I176" s="15"/>
       <c r="J176" s="15"/>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A177" s="15">
         <v>3176</v>
       </c>
@@ -29001,7 +29004,7 @@
       <c r="I177" s="15"/>
       <c r="J177" s="15"/>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A178" s="15">
         <v>3177</v>
       </c>
@@ -29021,7 +29024,7 @@
       <c r="I178" s="15"/>
       <c r="J178" s="15"/>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A179" s="15">
         <v>3178</v>
       </c>
@@ -29039,7 +29042,7 @@
       <c r="I179" s="15"/>
       <c r="J179" s="15"/>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A180" s="15">
         <v>3179</v>
       </c>
@@ -29059,7 +29062,7 @@
       <c r="I180" s="15"/>
       <c r="J180" s="15"/>
     </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A181" s="15">
         <v>3180</v>
       </c>
@@ -29077,7 +29080,7 @@
       <c r="I181" s="15"/>
       <c r="J181" s="15"/>
     </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A182" s="15">
         <v>3181</v>
       </c>
@@ -29095,7 +29098,7 @@
       <c r="I182" s="15"/>
       <c r="J182" s="15"/>
     </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A183" s="15">
         <v>3182</v>
       </c>
@@ -29113,7 +29116,7 @@
       <c r="I183" s="15"/>
       <c r="J183" s="15"/>
     </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="184" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A184" s="15">
         <v>3183</v>
       </c>
@@ -29133,7 +29136,7 @@
       <c r="I184" s="15"/>
       <c r="J184" s="15"/>
     </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="185" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A185" s="15">
         <v>3184</v>
       </c>
@@ -29153,7 +29156,7 @@
       <c r="I185" s="15"/>
       <c r="J185" s="15"/>
     </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="186" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A186" s="15">
         <v>3185</v>
       </c>
@@ -29171,7 +29174,7 @@
       <c r="I186" s="15"/>
       <c r="J186" s="15"/>
     </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="187" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A187" s="15">
         <v>3186</v>
       </c>
@@ -29193,7 +29196,7 @@
       <c r="I187" s="15"/>
       <c r="J187" s="15"/>
     </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="188" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A188" s="15">
         <v>3187</v>
       </c>
@@ -29213,7 +29216,7 @@
       <c r="I188" s="15"/>
       <c r="J188" s="15"/>
     </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="189" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A189" s="15">
         <v>3188</v>
       </c>
@@ -29237,7 +29240,7 @@
       <c r="I189" s="15"/>
       <c r="J189" s="15"/>
     </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="190" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A190" s="15">
         <v>3189</v>
       </c>
@@ -29259,7 +29262,7 @@
       <c r="I190" s="15"/>
       <c r="J190" s="15"/>
     </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="191" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A191" s="15">
         <v>3190</v>
       </c>
@@ -29281,7 +29284,7 @@
       <c r="I191" s="15"/>
       <c r="J191" s="15"/>
     </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A192" s="15">
         <v>3191</v>
       </c>
@@ -29305,7 +29308,7 @@
       <c r="I192" s="15"/>
       <c r="J192" s="15"/>
     </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A193" s="15">
         <v>3192</v>
       </c>
@@ -29327,7 +29330,7 @@
       <c r="I193" s="15"/>
       <c r="J193" s="15"/>
     </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A194" s="15">
         <v>3193</v>
       </c>
@@ -29345,7 +29348,7 @@
       <c r="I194" s="15"/>
       <c r="J194" s="15"/>
     </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A195" s="15">
         <v>3194</v>
       </c>
@@ -29363,7 +29366,7 @@
       <c r="I195" s="15"/>
       <c r="J195" s="15"/>
     </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A196" s="15">
         <v>3195</v>
       </c>
@@ -29385,7 +29388,7 @@
       <c r="I196" s="15"/>
       <c r="J196" s="15"/>
     </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A197" s="15">
         <v>3196</v>
       </c>
@@ -29405,7 +29408,7 @@
       <c r="I197" s="15"/>
       <c r="J197" s="15"/>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A198" s="15">
         <v>3197</v>
       </c>
@@ -29423,7 +29426,7 @@
       <c r="I198" s="15"/>
       <c r="J198" s="15"/>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A199" s="15">
         <v>3198</v>
       </c>
@@ -29443,7 +29446,7 @@
       <c r="I199" s="15"/>
       <c r="J199" s="15"/>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A200" s="15">
         <v>3199</v>
       </c>
@@ -29465,7 +29468,7 @@
       <c r="I200" s="15"/>
       <c r="J200" s="15"/>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A201" s="15">
         <v>3200</v>
       </c>
@@ -29485,7 +29488,7 @@
       <c r="I201" s="15"/>
       <c r="J201" s="15"/>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A202" s="15">
         <v>3201</v>
       </c>
@@ -29507,7 +29510,7 @@
       <c r="I202" s="15"/>
       <c r="J202" s="15"/>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A203" s="15">
         <v>3202</v>
       </c>
@@ -29525,7 +29528,7 @@
       <c r="I203" s="15"/>
       <c r="J203" s="15"/>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A204" s="15">
         <v>3203</v>
       </c>
@@ -29545,7 +29548,7 @@
       <c r="I204" s="15"/>
       <c r="J204" s="15"/>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A205" s="15">
         <v>3204</v>
       </c>
@@ -29565,7 +29568,7 @@
       <c r="I205" s="15"/>
       <c r="J205" s="15"/>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A206" s="15">
         <v>3205</v>
       </c>
@@ -29583,7 +29586,7 @@
       <c r="I206" s="15"/>
       <c r="J206" s="15"/>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A207" s="15">
         <v>3206</v>
       </c>
@@ -29601,7 +29604,7 @@
       <c r="I207" s="15"/>
       <c r="J207" s="15"/>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A208" s="15">
         <v>3207</v>
       </c>
@@ -29619,7 +29622,7 @@
       <c r="I208" s="15"/>
       <c r="J208" s="15"/>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A209" s="15">
         <v>3208</v>
       </c>
@@ -29637,7 +29640,7 @@
       <c r="I209" s="15"/>
       <c r="J209" s="15"/>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A210" s="15">
         <v>3209</v>
       </c>
@@ -29657,7 +29660,7 @@
       <c r="I210" s="15"/>
       <c r="J210" s="15"/>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A211" s="15">
         <v>3210</v>
       </c>
@@ -29675,7 +29678,7 @@
       <c r="I211" s="15"/>
       <c r="J211" s="15"/>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A212" s="15">
         <v>3211</v>
       </c>
@@ -29701,19 +29704,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6B13F65-1ED6-4D87-83E4-F30D307F48A0}">
   <dimension ref="A1:H52"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.41796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.15625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.83984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.83984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.26171875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.68359375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="53.41796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="53.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1060</v>
       </c>
@@ -29739,7 +29742,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1001</v>
       </c>
@@ -29765,7 +29768,7 @@
         <v>78701</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1002</v>
       </c>
@@ -29791,7 +29794,7 @@
         <v>78702</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1003</v>
       </c>
@@ -29817,7 +29820,7 @@
         <v>78703</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1004</v>
       </c>
@@ -29843,7 +29846,7 @@
         <v>78704</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>1005</v>
       </c>
@@ -29869,7 +29872,7 @@
         <v>78705</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>1006</v>
       </c>
@@ -29895,7 +29898,7 @@
         <v>78717</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>1007</v>
       </c>
@@ -29921,7 +29924,7 @@
         <v>78723</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>1008</v>
       </c>
@@ -29947,7 +29950,7 @@
         <v>78726</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>1009</v>
       </c>
@@ -29973,7 +29976,7 @@
         <v>78727</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>1010</v>
       </c>
@@ -29999,7 +30002,7 @@
         <v>78728</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>1011</v>
       </c>
@@ -30025,7 +30028,7 @@
         <v>78729</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>1012</v>
       </c>
@@ -30051,7 +30054,7 @@
         <v>78731</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>1013</v>
       </c>
@@ -30077,7 +30080,7 @@
         <v>78733</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>1014</v>
       </c>
@@ -30103,7 +30106,7 @@
         <v>78734</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>1015</v>
       </c>
@@ -30129,7 +30132,7 @@
         <v>78735</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>1016</v>
       </c>
@@ -30155,7 +30158,7 @@
         <v>78736</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>1017</v>
       </c>
@@ -30181,7 +30184,7 @@
         <v>78737</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>1018</v>
       </c>
@@ -30207,7 +30210,7 @@
         <v>78738</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>1019</v>
       </c>
@@ -30233,7 +30236,7 @@
         <v>78741</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>1020</v>
       </c>
@@ -30259,7 +30262,7 @@
         <v>78744</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>1021</v>
       </c>
@@ -30285,7 +30288,7 @@
         <v>78745</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>1022</v>
       </c>
@@ -30311,7 +30314,7 @@
         <v>78746</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>1023</v>
       </c>
@@ -30337,7 +30340,7 @@
         <v>78748</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>1024</v>
       </c>
@@ -30363,7 +30366,7 @@
         <v>78749</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>1025</v>
       </c>
@@ -30389,7 +30392,7 @@
         <v>78750</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>1026</v>
       </c>
@@ -30415,7 +30418,7 @@
         <v>77002</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>1027</v>
       </c>
@@ -30441,7 +30444,7 @@
         <v>77005</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>1028</v>
       </c>
@@ -30467,7 +30470,7 @@
         <v>75201</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>1029</v>
       </c>
@@ -30493,7 +30496,7 @@
         <v>75204</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>1030</v>
       </c>
@@ -30519,7 +30522,7 @@
         <v>78205</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>1031</v>
       </c>
@@ -30545,7 +30548,7 @@
         <v>78209</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>1032</v>
       </c>
@@ -30571,7 +30574,7 @@
         <v>76102</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>1033</v>
       </c>
@@ -30597,7 +30600,7 @@
         <v>75024</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>1034</v>
       </c>
@@ -30623,7 +30626,7 @@
         <v>79901</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>1035</v>
       </c>
@@ -30649,7 +30652,7 @@
         <v>78401</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>1036</v>
       </c>
@@ -30675,7 +30678,7 @@
         <v>90001</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>1037</v>
       </c>
@@ -30701,7 +30704,7 @@
         <v>90017</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>1038</v>
       </c>
@@ -30727,7 +30730,7 @@
         <v>94102</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>1039</v>
       </c>
@@ -30753,7 +30756,7 @@
         <v>92101</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>1040</v>
       </c>
@@ -30779,7 +30782,7 @@
         <v>95814</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>1041</v>
       </c>
@@ -30805,7 +30808,7 @@
         <v>10001</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>1042</v>
       </c>
@@ -30831,7 +30834,7 @@
         <v>10019</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>1043</v>
       </c>
@@ -30857,7 +30860,7 @@
         <v>60601</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>1044</v>
       </c>
@@ -30883,7 +30886,7 @@
         <v>60611</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>1045</v>
       </c>
@@ -30909,7 +30912,7 @@
         <v>33101</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>1046</v>
       </c>
@@ -30935,7 +30938,7 @@
         <v>32801</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>1047</v>
       </c>
@@ -30961,7 +30964,7 @@
         <v>30303</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>1048</v>
       </c>
@@ -30987,7 +30990,7 @@
         <v>98101</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>1049</v>
       </c>
@@ -31013,7 +31016,7 @@
         <v>80202</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>1050</v>
       </c>
@@ -31039,7 +31042,7 @@
         <v>1313</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="F52" s="1"/>
     </row>
   </sheetData>
@@ -31063,15 +31066,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AD044D4-4F87-4160-8364-E0E4EA576FBF}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.83984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.41796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>1314</v>
       </c>
@@ -31085,7 +31088,7 @@
         <v>1317</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="15">
         <v>1001</v>
       </c>
@@ -31099,7 +31102,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="15">
         <v>1002</v>
       </c>
@@ -31113,7 +31116,7 @@
         <v>1321</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="15">
         <v>1003</v>
       </c>
@@ -31127,7 +31130,7 @@
         <v>1323</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="15">
         <v>1004</v>
       </c>
@@ -31141,7 +31144,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="15">
         <v>1005</v>
       </c>
@@ -31155,7 +31158,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="15">
         <v>1006</v>
       </c>
@@ -31169,7 +31172,7 @@
         <v>1321</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="15">
         <v>1007</v>
       </c>
@@ -31183,7 +31186,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="15">
         <v>1008</v>
       </c>
@@ -31197,7 +31200,7 @@
         <v>1323</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="15">
         <v>1009</v>
       </c>
@@ -31211,7 +31214,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="15">
         <v>1010</v>
       </c>
@@ -31233,16 +31236,16 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{192F35C5-E820-446B-BEF5-BB51BAA4CC8B}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="18.26171875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.26171875" style="10" customWidth="1"/>
-    <col min="6" max="6" width="15.68359375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="34.68359375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.83984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" style="10" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="34.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1332</v>
       </c>
@@ -31271,7 +31274,7 @@
         <v>1337</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>212000</v>
       </c>
@@ -31291,7 +31294,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>212000</v>
       </c>
@@ -31311,7 +31314,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>212001</v>
       </c>
@@ -31335,7 +31338,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>212002</v>
       </c>
@@ -31358,7 +31361,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>212003</v>
       </c>
@@ -31378,7 +31381,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>212004</v>
       </c>
@@ -31404,7 +31407,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>212004</v>
       </c>
@@ -31430,7 +31433,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>212005</v>
       </c>
@@ -31450,7 +31453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>212006</v>
       </c>
@@ -31476,7 +31479,7 @@
         <v>1324</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>212007</v>
       </c>
@@ -31499,7 +31502,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>212007</v>
       </c>
@@ -31522,7 +31525,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>212008</v>
       </c>
@@ -31542,7 +31545,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>212008</v>
       </c>
@@ -31562,7 +31565,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>212009</v>
       </c>
@@ -31585,7 +31588,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>212010</v>
       </c>
@@ -31608,7 +31611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>212010</v>
       </c>
@@ -31631,7 +31634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>212011</v>
       </c>
@@ -31651,7 +31654,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>212012</v>
       </c>
@@ -31674,7 +31677,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>212013</v>
       </c>
@@ -31697,7 +31700,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>212013</v>
       </c>
@@ -31720,7 +31723,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>212014</v>
       </c>
@@ -31743,7 +31746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>212015</v>
       </c>
@@ -31766,7 +31769,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>212016</v>
       </c>
@@ -31789,7 +31792,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>212016</v>
       </c>
@@ -31812,7 +31815,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>212017</v>
       </c>
@@ -31835,7 +31838,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>212018</v>
       </c>
@@ -31861,7 +31864,7 @@
         <v>1342</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>212019</v>
       </c>
@@ -31884,7 +31887,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>212020</v>
       </c>
@@ -31907,7 +31910,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>212021</v>
       </c>
@@ -31930,7 +31933,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>212022</v>
       </c>
@@ -31953,7 +31956,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>212023</v>
       </c>
@@ -31973,7 +31976,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>212024</v>
       </c>
@@ -31993,7 +31996,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>212025</v>
       </c>
@@ -32017,7 +32020,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>212025</v>
       </c>
@@ -32041,20 +32044,20 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="H36" s="11"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="H37" s="11"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="H38" s="11"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="H39" s="11"/>
       <c r="J39" s="12"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="H40" s="11"/>
     </row>
   </sheetData>
@@ -32065,17 +32068,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB4E03EB-1D01-4D46-B67A-79D285C8BCC3}">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.41796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.83984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.68359375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.83984375" customWidth="1"/>
-    <col min="5" max="5" width="17.15625" customWidth="1"/>
-    <col min="6" max="6" width="19.83984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="17.1640625" customWidth="1"/>
+    <col min="6" max="6" width="19.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1061</v>
       </c>
@@ -32098,7 +32101,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1128</v>
       </c>
@@ -32121,7 +32124,7 @@
         <v>78701</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1346</v>
       </c>
@@ -32144,7 +32147,7 @@
         <v>78702</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>1352</v>
       </c>
@@ -32167,7 +32170,7 @@
         <v>78703</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>1237</v>
       </c>
@@ -32190,7 +32193,7 @@
         <v>78704</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>1363</v>
       </c>
@@ -32213,7 +32216,7 @@
         <v>78705</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>1369</v>
       </c>
@@ -32236,7 +32239,7 @@
         <v>78717</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>1374</v>
       </c>
@@ -32259,7 +32262,7 @@
         <v>78723</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>1379</v>
       </c>
@@ -32282,7 +32285,7 @@
         <v>78727</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>1385</v>
       </c>
@@ -32305,7 +32308,7 @@
         <v>78729</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>1390</v>
       </c>
@@ -32328,7 +32331,7 @@
         <v>78745</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>1068</v>
       </c>
@@ -32351,7 +32354,7 @@
         <v>77002</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>1400</v>
       </c>
@@ -32374,7 +32377,7 @@
         <v>75201</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>1406</v>
       </c>
@@ -32397,7 +32400,7 @@
         <v>78205</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>1412</v>
       </c>
@@ -32420,7 +32423,7 @@
         <v>76102</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>1418</v>
       </c>
@@ -32443,7 +32446,7 @@
         <v>90001</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>1424</v>
       </c>
@@ -32466,7 +32469,7 @@
         <v>94102</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>1430</v>
       </c>
@@ -32489,7 +32492,7 @@
         <v>10001</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>1212</v>
       </c>
@@ -32512,7 +32515,7 @@
         <v>60601</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>1440</v>
       </c>
@@ -32535,7 +32538,7 @@
         <v>33101</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>1280</v>
       </c>
@@ -32570,18 +32573,18 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{017E45DF-A8FC-4DA9-ADC7-BD6477880ABE}">
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.83984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.41796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.41796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.41796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1450</v>
       </c>
@@ -32600,11 +32603,11 @@
       <c r="F1" t="s">
         <v>1454</v>
       </c>
-      <c r="G1" s="23" t="s">
+      <c r="G1" t="s">
         <v>1063</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1069</v>
       </c>
@@ -32623,11 +32626,11 @@
       <c r="F2">
         <v>3395325649</v>
       </c>
-      <c r="G2" s="23" t="s">
+      <c r="G2" t="s">
         <v>1457</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1218</v>
       </c>
@@ -32646,11 +32649,11 @@
       <c r="F3">
         <v>2706602803</v>
       </c>
-      <c r="G3" s="23" t="s">
+      <c r="G3" t="s">
         <v>1460</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>1228</v>
       </c>
@@ -32669,11 +32672,11 @@
       <c r="F4">
         <v>4139645586</v>
       </c>
-      <c r="G4" s="23" t="s">
+      <c r="G4" t="s">
         <v>1463</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>1243</v>
       </c>
@@ -32692,7 +32695,7 @@
       <c r="F5">
         <v>7224308314</v>
       </c>
-      <c r="G5" s="23" t="s">
+      <c r="G5" t="s">
         <v>1466</v>
       </c>
     </row>
@@ -32704,17 +32707,17 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AE67A6D-9CC7-450D-88EA-5236F49D6A17}">
   <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.83984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.68359375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="71.68359375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.41796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="71.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>1467</v>
       </c>
@@ -32734,7 +32737,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="15" t="s">
         <v>1318</v>
       </c>
@@ -32754,7 +32757,7 @@
         <v>1474</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="15" t="s">
         <v>1318</v>
       </c>
@@ -32774,7 +32777,7 @@
         <v>1474</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="15" t="s">
         <v>1322</v>
       </c>
@@ -32794,7 +32797,7 @@
         <v>1474</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="15" t="s">
         <v>1320</v>
       </c>
@@ -32814,7 +32817,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="15" t="s">
         <v>1324</v>
       </c>
@@ -32834,7 +32837,7 @@
         <v>1474</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="15" t="s">
         <v>1324</v>
       </c>
@@ -32854,7 +32857,7 @@
         <v>1474</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="15" t="s">
         <v>1322</v>
       </c>
@@ -32874,7 +32877,7 @@
         <v>1474</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="15" t="s">
         <v>1324</v>
       </c>
@@ -32894,7 +32897,7 @@
         <v>1474</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="15" t="s">
         <v>1324</v>
       </c>
@@ -32914,7 +32917,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="15" t="s">
         <v>1320</v>
       </c>
@@ -32932,7 +32935,7 @@
         <v>1492</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="15" t="s">
         <v>1322</v>
       </c>
@@ -32950,7 +32953,7 @@
         <v>1492</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="15" t="s">
         <v>1322</v>
       </c>
@@ -32970,7 +32973,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="15"/>
       <c r="B14" s="15"/>
       <c r="C14" s="15"/>
@@ -32978,25 +32981,25 @@
       <c r="E14" s="15"/>
       <c r="F14" s="15"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="D15" s="10"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="D16" s="10"/>
     </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C17" s="10"/>
     </row>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C18" s="10"/>
     </row>
-    <row r="19" spans="3:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C19" s="10"/>
     </row>
-    <row r="21" spans="3:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="3:4" x14ac:dyDescent="0.2">
       <c r="D21" s="10"/>
     </row>
-    <row r="22" spans="3:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="3:4" x14ac:dyDescent="0.2">
       <c r="D22" s="10"/>
     </row>
   </sheetData>
